--- a/Tổng hợp Bộ đề thi/Câu hỏi chuyên môn Soát vé.xlsx
+++ b/Tổng hợp Bộ đề thi/Câu hỏi chuyên môn Soát vé.xlsx
@@ -8,16 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/764b92bfa4480aa4/Claude/Website ôn thi Nghị Quyết/Tổng hợp Bộ đề thi/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{E2E8628D-81AC-6644-9E18-F131E352B14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F56A2EB-306D-1A4E-A9AB-A39CDD62B746}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{E2E8628D-81AC-6644-9E18-F131E352B14B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB3FCDD3-DC55-D14C-BEEB-AE0E09CBDBBD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20320" tabRatio="812" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="34200" windowHeight="20320" tabRatio="812" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SV" sheetId="2" r:id="rId1"/>
-    <sheet name="CM03_An toàn chung - VH" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'CM03_An toàn chung - VH'!$A$6:$O$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SV!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -41,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="531">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="518">
   <si>
     <t>Mã câu hỏi
 (Theo quy định)</t>
@@ -1432,57 +1430,6 @@
     <t>Nhận giữ hộ vé do hướng dẫn viên cần qua cổng trước, lát nữa khách của hướng dẫn viên sẽ đến lấy sau.</t>
   </si>
   <si>
-    <t>MẪU NHẬP NGÂN HÀNG CÂU HỎI</t>
-  </si>
-  <si>
-    <t>MẪU 2 - NỘI DUNG CÂU HỎI SÁT HẠCH CHUYÊN MÔN 2024</t>
-  </si>
-  <si>
-    <t>Lĩnh vực:</t>
-  </si>
-  <si>
-    <t>Vận hành dịch vụ khách hàng</t>
-  </si>
-  <si>
-    <t>Người soạn đề:</t>
-  </si>
-  <si>
-    <t>Nhóm HĐCM</t>
-  </si>
-  <si>
-    <t>Loại kiến thức (Chuyên môn/nghiệp vụ)</t>
-  </si>
-  <si>
-    <t>Độ khó
-(chọn giá trị gán sẵn)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Ghi chú
-</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(Tick X nếu là câu hỏi mới)</t>
-    </r>
-  </si>
-  <si>
-    <t>Ghi chú</t>
-  </si>
-  <si>
-    <t>Chuyên môn 3
-An toàn chung - Vận hành</t>
-  </si>
-  <si>
-    <t>SWG-ST-HB-04 Sổ tay định hướng về an toàn cho nhân viên mới (sửa đổi lần 01)</t>
-  </si>
-  <si>
     <t>Khi có người bị thương, ai là người đóng vai trò quan trọng trong việc đảm bảo cho Khách hàng và đồng nghiệp luôn được chăm sóc chu đáo?</t>
   </si>
   <si>
@@ -1538,9 +1485,6 @@
   </si>
   <si>
     <t>Ngăn chặn các bài viết với thông tin về sự cố có ảnh hưởng tiêu cực đến công ty.</t>
-  </si>
-  <si>
-    <t>X</t>
   </si>
   <si>
     <t>Theo Sổ tay định hướng về An toàn cho nhân viên mới, đối với khách hàng thì SẠCH có nghĩa là gì?</t>
@@ -1691,7 +1635,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1712,12 +1656,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="0"/>
@@ -1725,43 +1663,8 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1810,7 +1713,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1820,12 +1723,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1854,32 +1751,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="18">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2100,69 +1977,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2172,196 +1998,190 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="8" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2369,108 +2189,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2805,3034 +2524,3034 @@
   <dimension ref="A1:K121"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="15" style="23" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5" style="23" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5" style="23" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="31.83203125" style="23" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="6.1640625" style="26" customWidth="1"/>
-    <col min="6" max="6" width="81" style="32" customWidth="1"/>
-    <col min="7" max="7" width="11.83203125" style="28" customWidth="1"/>
-    <col min="8" max="11" width="36.5" style="27" customWidth="1"/>
-    <col min="12" max="16384" width="9.1640625" style="23"/>
+    <col min="1" max="1" width="15" style="4" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5" style="4" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" style="4" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="31.83203125" style="4" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="6.1640625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="81" style="10" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" style="7" customWidth="1"/>
+    <col min="8" max="11" width="36.5" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="9.1640625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="19" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:11" s="3" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="46" t="s">
+      <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="47" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="46" t="s">
+      <c r="G1" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="48" t="s">
+      <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="48" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="48" t="s">
+      <c r="J1" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="48" t="s">
+      <c r="K1" s="26" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="30" customFormat="1" ht="76" x14ac:dyDescent="0.15">
-      <c r="A2" s="33"/>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="49">
+    <row r="2" spans="1:11" s="8" customFormat="1" ht="76" x14ac:dyDescent="0.15">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="27">
         <v>1</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="F2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="49">
+      <c r="G2" s="27">
         <v>1</v>
       </c>
-      <c r="H2" s="80" t="s">
+      <c r="H2" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="51" t="s">
+      <c r="I2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="51" t="s">
+      <c r="J2" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="51" t="s">
+      <c r="K2" s="29" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="A3" s="33"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
-      <c r="D3" s="36"/>
-      <c r="E3" s="49">
+    <row r="3" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="A3" s="11"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="27">
         <v>2</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="49">
+      <c r="G3" s="27">
         <v>3</v>
       </c>
-      <c r="H3" s="51" t="s">
+      <c r="H3" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="51" t="s">
+      <c r="I3" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="80" t="s">
+      <c r="J3" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="K3" s="51" t="s">
+      <c r="K3" s="29" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:11" s="30" customFormat="1" ht="19" x14ac:dyDescent="0.15">
-      <c r="A4" s="33"/>
-      <c r="B4" s="35"/>
-      <c r="C4" s="35"/>
-      <c r="D4" s="36"/>
-      <c r="E4" s="49">
+    <row r="4" spans="1:11" s="8" customFormat="1" ht="19" x14ac:dyDescent="0.15">
+      <c r="A4" s="11"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="27">
         <v>3</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="49">
+      <c r="G4" s="27">
         <v>4</v>
       </c>
-      <c r="H4" s="51" t="s">
+      <c r="H4" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="51" t="s">
+      <c r="I4" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="51" t="s">
+      <c r="J4" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="80" t="s">
+      <c r="K4" s="58" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="A5" s="33"/>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="36"/>
-      <c r="E5" s="49">
+    <row r="5" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="A5" s="11"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="27">
         <v>4</v>
       </c>
-      <c r="F5" s="50" t="s">
+      <c r="F5" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="49">
+      <c r="G5" s="27">
         <v>1</v>
       </c>
-      <c r="H5" s="80" t="s">
+      <c r="H5" s="58" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="51" t="s">
+      <c r="I5" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="J5" s="51" t="s">
+      <c r="J5" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="51" t="s">
+      <c r="K5" s="29" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E6" s="49">
+    <row r="6" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E6" s="27">
         <v>5</v>
       </c>
-      <c r="F6" s="50" t="s">
+      <c r="F6" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="49">
+      <c r="G6" s="27">
         <v>3</v>
       </c>
-      <c r="H6" s="51" t="s">
+      <c r="H6" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="I6" s="51" t="s">
+      <c r="I6" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="J6" s="80" t="s">
+      <c r="J6" s="58" t="s">
         <v>34</v>
       </c>
-      <c r="K6" s="51" t="s">
+      <c r="K6" s="29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E7" s="49">
+    <row r="7" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E7" s="27">
         <v>6</v>
       </c>
-      <c r="F7" s="50" t="s">
+      <c r="F7" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="G7" s="49">
+      <c r="G7" s="27">
         <v>4</v>
       </c>
-      <c r="H7" s="51" t="s">
+      <c r="H7" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="51" t="s">
+      <c r="I7" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="51" t="s">
+      <c r="J7" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="80" t="s">
+      <c r="K7" s="58" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E8" s="49">
+    <row r="8" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E8" s="27">
         <v>7</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="G8" s="49">
+      <c r="G8" s="27">
         <v>2</v>
       </c>
-      <c r="H8" s="51" t="s">
+      <c r="H8" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="I8" s="80" t="s">
+      <c r="I8" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="J8" s="51" t="s">
+      <c r="J8" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="51" t="s">
+      <c r="K8" s="29" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E9" s="49">
+    <row r="9" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E9" s="27">
         <v>8</v>
       </c>
-      <c r="F9" s="50" t="s">
+      <c r="F9" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="G9" s="49">
+      <c r="G9" s="27">
         <v>1</v>
       </c>
-      <c r="H9" s="80" t="s">
+      <c r="H9" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="I9" s="51" t="s">
+      <c r="I9" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="J9" s="51" t="s">
+      <c r="J9" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="K9" s="51" t="s">
+      <c r="K9" s="29" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E10" s="49">
+    <row r="10" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E10" s="27">
         <v>9</v>
       </c>
-      <c r="F10" s="50" t="s">
+      <c r="F10" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="27">
         <v>3</v>
       </c>
-      <c r="H10" s="51">
+      <c r="H10" s="29">
         <v>6</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="29">
         <v>7</v>
       </c>
-      <c r="J10" s="80">
+      <c r="J10" s="58">
         <v>8</v>
       </c>
-      <c r="K10" s="51">
+      <c r="K10" s="29">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E11" s="49">
+    <row r="11" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E11" s="27">
         <v>10</v>
       </c>
-      <c r="F11" s="50" t="s">
+      <c r="F11" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="49">
+      <c r="G11" s="27">
         <v>1</v>
       </c>
-      <c r="H11" s="80" t="s">
+      <c r="H11" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="I11" s="51" t="s">
+      <c r="I11" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="J11" s="51" t="s">
+      <c r="J11" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="K11" s="51" t="s">
+      <c r="K11" s="29" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E12" s="49">
+    <row r="12" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E12" s="27">
         <v>11</v>
       </c>
-      <c r="F12" s="50" t="s">
+      <c r="F12" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="G12" s="49">
+      <c r="G12" s="27">
         <v>1</v>
       </c>
-      <c r="H12" s="80" t="s">
+      <c r="H12" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="51" t="s">
+      <c r="I12" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="J12" s="51" t="s">
+      <c r="J12" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="K12" s="51" t="s">
+      <c r="K12" s="29" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E13" s="49">
+    <row r="13" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E13" s="27">
         <v>12</v>
       </c>
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="G13" s="49">
+      <c r="G13" s="27">
         <v>4</v>
       </c>
-      <c r="H13" s="51" t="s">
+      <c r="H13" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="I13" s="51" t="s">
+      <c r="I13" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="J13" s="51" t="s">
+      <c r="J13" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="K13" s="80" t="s">
+      <c r="K13" s="58" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E14" s="49">
+    <row r="14" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E14" s="27">
         <v>13</v>
       </c>
-      <c r="F14" s="50" t="s">
+      <c r="F14" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="49">
+      <c r="G14" s="27">
         <v>2</v>
       </c>
-      <c r="H14" s="51" t="s">
+      <c r="H14" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="I14" s="80" t="s">
+      <c r="I14" s="58" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="51" t="s">
+      <c r="J14" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="K14" s="51" t="s">
+      <c r="K14" s="29" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E15" s="49">
+    <row r="15" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E15" s="27">
         <v>14</v>
       </c>
-      <c r="F15" s="50" t="s">
+      <c r="F15" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="49">
+      <c r="G15" s="27">
         <v>4</v>
       </c>
-      <c r="H15" s="51" t="s">
+      <c r="H15" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="I15" s="51" t="s">
+      <c r="I15" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="J15" s="51" t="s">
+      <c r="J15" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="K15" s="80" t="s">
+      <c r="K15" s="58" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:11" s="30" customFormat="1" ht="76" x14ac:dyDescent="0.15">
-      <c r="E16" s="49">
+    <row r="16" spans="1:11" s="8" customFormat="1" ht="76" x14ac:dyDescent="0.15">
+      <c r="E16" s="27">
         <v>15</v>
       </c>
-      <c r="F16" s="50" t="s">
+      <c r="F16" s="28" t="s">
         <v>68</v>
       </c>
-      <c r="G16" s="49">
+      <c r="G16" s="27">
         <v>1</v>
       </c>
-      <c r="H16" s="80" t="s">
+      <c r="H16" s="58" t="s">
         <v>69</v>
       </c>
-      <c r="I16" s="51" t="s">
+      <c r="I16" s="29" t="s">
         <v>70</v>
       </c>
-      <c r="J16" s="51" t="s">
+      <c r="J16" s="29" t="s">
         <v>71</v>
       </c>
-      <c r="K16" s="51" t="s">
+      <c r="K16" s="29" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E17" s="49">
+    <row r="17" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E17" s="27">
         <v>16</v>
       </c>
-      <c r="F17" s="50" t="s">
+      <c r="F17" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="G17" s="49">
+      <c r="G17" s="27">
         <v>1</v>
       </c>
-      <c r="H17" s="80" t="s">
+      <c r="H17" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="I17" s="51" t="s">
+      <c r="I17" s="29" t="s">
         <v>75</v>
       </c>
-      <c r="J17" s="51" t="s">
+      <c r="J17" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="K17" s="51" t="s">
+      <c r="K17" s="29" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E18" s="49">
+    <row r="18" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E18" s="27">
         <v>17</v>
       </c>
-      <c r="F18" s="50" t="s">
+      <c r="F18" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="G18" s="49">
+      <c r="G18" s="27">
         <v>3</v>
       </c>
-      <c r="H18" s="51" t="s">
+      <c r="H18" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="I18" s="51" t="s">
+      <c r="I18" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="J18" s="80" t="s">
+      <c r="J18" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="K18" s="51" t="s">
+      <c r="K18" s="29" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="19" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E19" s="49">
+    <row r="19" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E19" s="27">
         <v>18</v>
       </c>
-      <c r="F19" s="50" t="s">
+      <c r="F19" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="G19" s="49">
+      <c r="G19" s="27">
         <v>2</v>
       </c>
-      <c r="H19" s="51" t="s">
+      <c r="H19" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="I19" s="80" t="s">
+      <c r="I19" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="J19" s="51" t="s">
+      <c r="J19" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="K19" s="51" t="s">
+      <c r="K19" s="29" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="20" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E20" s="49">
+    <row r="20" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E20" s="27">
         <v>19</v>
       </c>
-      <c r="F20" s="52" t="s">
+      <c r="F20" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="G20" s="53">
+      <c r="G20" s="31">
         <v>3</v>
       </c>
-      <c r="H20" s="54" t="s">
+      <c r="H20" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="I20" s="54" t="s">
+      <c r="I20" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="J20" s="81" t="s">
+      <c r="J20" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="K20" s="54" t="s">
+      <c r="K20" s="32" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E21" s="49">
+    <row r="21" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E21" s="27">
         <v>20</v>
       </c>
-      <c r="F21" s="55" t="s">
+      <c r="F21" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="G21" s="56">
+      <c r="G21" s="34">
         <v>3</v>
       </c>
-      <c r="H21" s="57" t="s">
+      <c r="H21" s="35" t="s">
         <v>90</v>
       </c>
-      <c r="I21" s="57" t="s">
+      <c r="I21" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="J21" s="82" t="s">
+      <c r="J21" s="60" t="s">
         <v>92</v>
       </c>
-      <c r="K21" s="57" t="s">
+      <c r="K21" s="35" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="22" spans="1:11" s="31" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E22" s="49">
+    <row r="22" spans="1:11" s="9" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E22" s="27">
         <v>21</v>
       </c>
-      <c r="F22" s="58" t="s">
+      <c r="F22" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="G22" s="59">
+      <c r="G22" s="37">
         <v>4</v>
       </c>
-      <c r="H22" s="60" t="s">
+      <c r="H22" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="I22" s="60" t="s">
+      <c r="I22" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="J22" s="60" t="s">
+      <c r="J22" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="K22" s="83" t="s">
+      <c r="K22" s="61" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="A23" s="33"/>
-      <c r="B23" s="33"/>
-      <c r="C23" s="33"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="49">
+    <row r="23" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="27">
         <v>22</v>
       </c>
-      <c r="F23" s="50" t="s">
+      <c r="F23" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="G23" s="49">
+      <c r="G23" s="27">
         <v>1</v>
       </c>
-      <c r="H23" s="80" t="s">
+      <c r="H23" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="I23" s="51" t="s">
+      <c r="I23" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="J23" s="51" t="s">
+      <c r="J23" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="K23" s="51" t="s">
+      <c r="K23" s="29" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="A24" s="33"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="36"/>
-      <c r="E24" s="49">
+    <row r="24" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="A24" s="11"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="27">
         <v>23</v>
       </c>
-      <c r="F24" s="50" t="s">
+      <c r="F24" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="G24" s="49">
+      <c r="G24" s="27">
         <v>4</v>
       </c>
-      <c r="H24" s="51" t="s">
+      <c r="H24" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="I24" s="51" t="s">
+      <c r="I24" s="29" t="s">
         <v>106</v>
       </c>
-      <c r="J24" s="51" t="s">
+      <c r="J24" s="29" t="s">
         <v>107</v>
       </c>
-      <c r="K24" s="80" t="s">
+      <c r="K24" s="58" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="25" spans="1:11" s="30" customFormat="1" ht="133" x14ac:dyDescent="0.15">
-      <c r="A25" s="33"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="36"/>
-      <c r="E25" s="49">
+    <row r="25" spans="1:11" s="8" customFormat="1" ht="133" x14ac:dyDescent="0.15">
+      <c r="A25" s="11"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="27">
         <v>24</v>
       </c>
-      <c r="F25" s="50" t="s">
+      <c r="F25" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="49">
+      <c r="G25" s="27">
         <v>1</v>
       </c>
-      <c r="H25" s="80" t="s">
+      <c r="H25" s="58" t="s">
         <v>110</v>
       </c>
-      <c r="I25" s="51" t="s">
+      <c r="I25" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="J25" s="51" t="s">
+      <c r="J25" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="K25" s="51" t="s">
+      <c r="K25" s="29" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="26" spans="1:11" s="30" customFormat="1" ht="19" x14ac:dyDescent="0.15">
-      <c r="A26" s="33"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
-      <c r="D26" s="36"/>
-      <c r="E26" s="49">
+    <row r="26" spans="1:11" s="8" customFormat="1" ht="19" x14ac:dyDescent="0.15">
+      <c r="A26" s="11"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="27">
         <v>25</v>
       </c>
-      <c r="F26" s="50" t="s">
+      <c r="F26" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="G26" s="49">
+      <c r="G26" s="27">
         <v>1</v>
       </c>
-      <c r="H26" s="80" t="s">
+      <c r="H26" s="58" t="s">
         <v>115</v>
       </c>
-      <c r="I26" s="51" t="s">
+      <c r="I26" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="J26" s="51" t="s">
+      <c r="J26" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="K26" s="51" t="s">
+      <c r="K26" s="29" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E27" s="49">
+    <row r="27" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E27" s="27">
         <v>26</v>
       </c>
-      <c r="F27" s="50" t="s">
+      <c r="F27" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="G27" s="49">
+      <c r="G27" s="27">
         <v>1</v>
       </c>
-      <c r="H27" s="80" t="s">
+      <c r="H27" s="58" t="s">
         <v>120</v>
       </c>
-      <c r="I27" s="51" t="s">
+      <c r="I27" s="29" t="s">
         <v>121</v>
       </c>
-      <c r="J27" s="51" t="s">
+      <c r="J27" s="29" t="s">
         <v>122</v>
       </c>
-      <c r="K27" s="51" t="s">
+      <c r="K27" s="29" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="28" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E28" s="49">
+    <row r="28" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E28" s="27">
         <v>27</v>
       </c>
-      <c r="F28" s="50" t="s">
+      <c r="F28" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="G28" s="49">
+      <c r="G28" s="27">
         <v>1</v>
       </c>
-      <c r="H28" s="80" t="s">
+      <c r="H28" s="58" t="s">
         <v>125</v>
       </c>
-      <c r="I28" s="51" t="s">
+      <c r="I28" s="29" t="s">
         <v>126</v>
       </c>
-      <c r="J28" s="51" t="s">
+      <c r="J28" s="29" t="s">
         <v>127</v>
       </c>
-      <c r="K28" s="51" t="s">
+      <c r="K28" s="29" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="29" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E29" s="49">
+    <row r="29" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E29" s="27">
         <v>28</v>
       </c>
-      <c r="F29" s="50" t="s">
+      <c r="F29" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="G29" s="49">
+      <c r="G29" s="27">
         <v>3</v>
       </c>
-      <c r="H29" s="51" t="s">
+      <c r="H29" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="I29" s="51" t="s">
+      <c r="I29" s="29" t="s">
         <v>131</v>
       </c>
-      <c r="J29" s="80" t="s">
+      <c r="J29" s="58" t="s">
         <v>132</v>
       </c>
-      <c r="K29" s="51" t="s">
+      <c r="K29" s="29" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E30" s="49">
+    <row r="30" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E30" s="27">
         <v>29</v>
       </c>
-      <c r="F30" s="50" t="s">
+      <c r="F30" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="G30" s="49">
+      <c r="G30" s="27">
         <v>2</v>
       </c>
-      <c r="H30" s="51" t="s">
+      <c r="H30" s="29" t="s">
         <v>135</v>
       </c>
-      <c r="I30" s="80" t="s">
+      <c r="I30" s="58" t="s">
         <v>136</v>
       </c>
-      <c r="J30" s="51" t="s">
+      <c r="J30" s="29" t="s">
         <v>137</v>
       </c>
-      <c r="K30" s="51" t="s">
+      <c r="K30" s="29" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:11" s="30" customFormat="1" ht="133" x14ac:dyDescent="0.15">
-      <c r="E31" s="49">
+    <row r="31" spans="1:11" s="8" customFormat="1" ht="133" x14ac:dyDescent="0.15">
+      <c r="E31" s="27">
         <v>30</v>
       </c>
-      <c r="F31" s="50" t="s">
+      <c r="F31" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="G31" s="49">
+      <c r="G31" s="27">
         <v>2</v>
       </c>
-      <c r="H31" s="51" t="s">
+      <c r="H31" s="29" t="s">
         <v>140</v>
       </c>
-      <c r="I31" s="80" t="s">
+      <c r="I31" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="J31" s="51" t="s">
+      <c r="J31" s="29" t="s">
         <v>142</v>
       </c>
-      <c r="K31" s="51" t="s">
+      <c r="K31" s="29" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="32" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E32" s="49">
+    <row r="32" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E32" s="27">
         <v>31</v>
       </c>
-      <c r="F32" s="50" t="s">
+      <c r="F32" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="G32" s="49">
+      <c r="G32" s="27">
         <v>4</v>
       </c>
-      <c r="H32" s="51" t="s">
+      <c r="H32" s="29" t="s">
         <v>145</v>
       </c>
-      <c r="I32" s="51" t="s">
+      <c r="I32" s="29" t="s">
         <v>146</v>
       </c>
-      <c r="J32" s="51" t="s">
+      <c r="J32" s="29" t="s">
         <v>147</v>
       </c>
-      <c r="K32" s="80" t="s">
+      <c r="K32" s="58" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="33" spans="1:11" s="30" customFormat="1" ht="114" x14ac:dyDescent="0.15">
-      <c r="E33" s="49">
+    <row r="33" spans="1:11" s="8" customFormat="1" ht="114" x14ac:dyDescent="0.15">
+      <c r="E33" s="27">
         <v>32</v>
       </c>
-      <c r="F33" s="52" t="s">
+      <c r="F33" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="G33" s="53">
+      <c r="G33" s="31">
         <v>3</v>
       </c>
-      <c r="H33" s="54" t="s">
+      <c r="H33" s="32" t="s">
         <v>150</v>
       </c>
-      <c r="I33" s="54" t="s">
+      <c r="I33" s="32" t="s">
         <v>151</v>
       </c>
-      <c r="J33" s="81" t="s">
+      <c r="J33" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="K33" s="54" t="s">
+      <c r="K33" s="32" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="34" spans="1:11" s="30" customFormat="1" ht="228" x14ac:dyDescent="0.15">
-      <c r="E34" s="49">
+    <row r="34" spans="1:11" s="8" customFormat="1" ht="228" x14ac:dyDescent="0.15">
+      <c r="E34" s="27">
         <v>33</v>
       </c>
-      <c r="F34" s="52" t="s">
+      <c r="F34" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="G34" s="53">
+      <c r="G34" s="31">
         <v>1</v>
       </c>
-      <c r="H34" s="81" t="s">
+      <c r="H34" s="59" t="s">
         <v>155</v>
       </c>
-      <c r="I34" s="54" t="s">
+      <c r="I34" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="J34" s="54" t="s">
+      <c r="J34" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="K34" s="54" t="s">
+      <c r="K34" s="32" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="35" spans="1:11" s="30" customFormat="1" ht="152" x14ac:dyDescent="0.15">
-      <c r="E35" s="49">
+    <row r="35" spans="1:11" s="8" customFormat="1" ht="152" x14ac:dyDescent="0.15">
+      <c r="E35" s="27">
         <v>34</v>
       </c>
-      <c r="F35" s="50" t="s">
+      <c r="F35" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="G35" s="49">
+      <c r="G35" s="27">
         <v>2</v>
       </c>
-      <c r="H35" s="51" t="s">
+      <c r="H35" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="I35" s="80" t="s">
+      <c r="I35" s="58" t="s">
         <v>161</v>
       </c>
-      <c r="J35" s="51" t="s">
+      <c r="J35" s="29" t="s">
         <v>162</v>
       </c>
-      <c r="K35" s="51" t="s">
+      <c r="K35" s="29" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="36" spans="1:11" s="30" customFormat="1" ht="171" x14ac:dyDescent="0.15">
-      <c r="E36" s="49">
+    <row r="36" spans="1:11" s="8" customFormat="1" ht="171" x14ac:dyDescent="0.15">
+      <c r="E36" s="27">
         <v>35</v>
       </c>
-      <c r="F36" s="50" t="s">
+      <c r="F36" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="G36" s="49">
+      <c r="G36" s="27">
         <v>2</v>
       </c>
-      <c r="H36" s="51" t="s">
+      <c r="H36" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="I36" s="80" t="s">
+      <c r="I36" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="J36" s="51" t="s">
+      <c r="J36" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="K36" s="51" t="s">
+      <c r="K36" s="29" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="37" spans="1:11" s="30" customFormat="1" ht="76" x14ac:dyDescent="0.15">
-      <c r="E37" s="49">
+    <row r="37" spans="1:11" s="8" customFormat="1" ht="76" x14ac:dyDescent="0.15">
+      <c r="E37" s="27">
         <v>36</v>
       </c>
-      <c r="F37" s="61" t="s">
+      <c r="F37" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="G37" s="62">
+      <c r="G37" s="40">
         <v>4</v>
       </c>
-      <c r="H37" s="63" t="s">
+      <c r="H37" s="41" t="s">
         <v>170</v>
       </c>
-      <c r="I37" s="63" t="s">
+      <c r="I37" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="J37" s="63" t="s">
+      <c r="J37" s="41" t="s">
         <v>172</v>
       </c>
-      <c r="K37" s="84" t="s">
+      <c r="K37" s="62" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="1:11" s="30" customFormat="1" ht="133" x14ac:dyDescent="0.15">
-      <c r="E38" s="49">
+    <row r="38" spans="1:11" s="8" customFormat="1" ht="133" x14ac:dyDescent="0.15">
+      <c r="E38" s="27">
         <v>37</v>
       </c>
-      <c r="F38" s="64" t="s">
+      <c r="F38" s="42" t="s">
         <v>174</v>
       </c>
-      <c r="G38" s="62">
+      <c r="G38" s="40">
         <v>1</v>
       </c>
-      <c r="H38" s="85" t="s">
+      <c r="H38" s="63" t="s">
         <v>175</v>
       </c>
-      <c r="I38" s="63" t="s">
+      <c r="I38" s="41" t="s">
         <v>176</v>
       </c>
-      <c r="J38" s="63" t="s">
+      <c r="J38" s="41" t="s">
         <v>177</v>
       </c>
-      <c r="K38" s="63" t="s">
+      <c r="K38" s="41" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="39" spans="1:11" s="37" customFormat="1" ht="38" x14ac:dyDescent="0.2">
-      <c r="A39" s="40"/>
-      <c r="B39" s="40"/>
-      <c r="C39" s="40"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="49">
+    <row r="39" spans="1:11" s="15" customFormat="1" ht="38" x14ac:dyDescent="0.2">
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="27">
         <v>38</v>
       </c>
-      <c r="F39" s="65" t="s">
+      <c r="F39" s="43" t="s">
         <v>179</v>
       </c>
-      <c r="G39" s="66">
+      <c r="G39" s="44">
         <v>4</v>
       </c>
-      <c r="H39" s="67" t="s">
+      <c r="H39" s="45" t="s">
         <v>180</v>
       </c>
-      <c r="I39" s="67" t="s">
+      <c r="I39" s="45" t="s">
         <v>181</v>
       </c>
-      <c r="J39" s="67" t="s">
+      <c r="J39" s="45" t="s">
         <v>182</v>
       </c>
-      <c r="K39" s="86" t="s">
+      <c r="K39" s="64" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="40" spans="1:11" s="37" customFormat="1" ht="38" x14ac:dyDescent="0.2">
-      <c r="A40" s="40"/>
-      <c r="B40" s="40"/>
-      <c r="C40" s="40"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="49">
+    <row r="40" spans="1:11" s="15" customFormat="1" ht="38" x14ac:dyDescent="0.2">
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="18"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="27">
         <v>39</v>
       </c>
-      <c r="F40" s="65" t="s">
+      <c r="F40" s="43" t="s">
         <v>184</v>
       </c>
-      <c r="G40" s="66">
+      <c r="G40" s="44">
         <v>4</v>
       </c>
-      <c r="H40" s="67" t="s">
+      <c r="H40" s="45" t="s">
         <v>185</v>
       </c>
-      <c r="I40" s="67" t="s">
+      <c r="I40" s="45" t="s">
         <v>186</v>
       </c>
-      <c r="J40" s="67" t="s">
+      <c r="J40" s="45" t="s">
         <v>187</v>
       </c>
-      <c r="K40" s="86" t="s">
+      <c r="K40" s="64" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="41" spans="1:11" s="37" customFormat="1" ht="38" x14ac:dyDescent="0.2">
-      <c r="A41" s="40"/>
-      <c r="B41" s="42"/>
-      <c r="C41" s="42"/>
-      <c r="D41" s="43"/>
-      <c r="E41" s="49">
+    <row r="41" spans="1:11" s="15" customFormat="1" ht="38" x14ac:dyDescent="0.2">
+      <c r="A41" s="18"/>
+      <c r="B41" s="20"/>
+      <c r="C41" s="20"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="27">
         <v>40</v>
       </c>
-      <c r="F41" s="65" t="s">
+      <c r="F41" s="43" t="s">
         <v>189</v>
       </c>
-      <c r="G41" s="66">
+      <c r="G41" s="44">
         <v>4</v>
       </c>
-      <c r="H41" s="67" t="s">
+      <c r="H41" s="45" t="s">
         <v>190</v>
       </c>
-      <c r="I41" s="67" t="s">
+      <c r="I41" s="45" t="s">
         <v>191</v>
       </c>
-      <c r="J41" s="67" t="s">
+      <c r="J41" s="45" t="s">
         <v>192</v>
       </c>
-      <c r="K41" s="86" t="s">
+      <c r="K41" s="64" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="42" spans="1:11" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.2">
-      <c r="A42" s="40"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="42"/>
-      <c r="D42" s="43"/>
-      <c r="E42" s="49">
+    <row r="42" spans="1:11" s="15" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+      <c r="A42" s="18"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="27">
         <v>41</v>
       </c>
-      <c r="F42" s="65" t="s">
+      <c r="F42" s="43" t="s">
         <v>194</v>
       </c>
-      <c r="G42" s="66">
+      <c r="G42" s="44">
         <v>1</v>
       </c>
-      <c r="H42" s="87" t="s">
+      <c r="H42" s="65" t="s">
         <v>195</v>
       </c>
-      <c r="I42" s="67" t="s">
+      <c r="I42" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="J42" s="67" t="s">
+      <c r="J42" s="45" t="s">
         <v>197</v>
       </c>
-      <c r="K42" s="68" t="s">
+      <c r="K42" s="46" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="43" spans="1:11" s="37" customFormat="1" ht="38" x14ac:dyDescent="0.2">
-      <c r="A43" s="44"/>
-      <c r="B43" s="44"/>
-      <c r="C43" s="44"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="49">
+    <row r="43" spans="1:11" s="15" customFormat="1" ht="38" x14ac:dyDescent="0.2">
+      <c r="A43" s="22"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="27">
         <v>42</v>
       </c>
-      <c r="F43" s="65" t="s">
+      <c r="F43" s="43" t="s">
         <v>199</v>
       </c>
-      <c r="G43" s="66">
+      <c r="G43" s="44">
         <v>1</v>
       </c>
-      <c r="H43" s="87" t="s">
+      <c r="H43" s="65" t="s">
         <v>200</v>
       </c>
-      <c r="I43" s="67" t="s">
+      <c r="I43" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="J43" s="67" t="s">
+      <c r="J43" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="K43" s="68" t="s">
+      <c r="K43" s="46" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:11" s="37" customFormat="1" ht="38" x14ac:dyDescent="0.2">
-      <c r="A44" s="44"/>
-      <c r="B44" s="44"/>
-      <c r="C44" s="44"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="49">
+    <row r="44" spans="1:11" s="15" customFormat="1" ht="38" x14ac:dyDescent="0.2">
+      <c r="A44" s="22"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="27">
         <v>43</v>
       </c>
-      <c r="F44" s="65" t="s">
+      <c r="F44" s="43" t="s">
         <v>204</v>
       </c>
-      <c r="G44" s="66">
+      <c r="G44" s="44">
         <v>4</v>
       </c>
-      <c r="H44" s="67" t="s">
+      <c r="H44" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="I44" s="67" t="s">
+      <c r="I44" s="45" t="s">
         <v>201</v>
       </c>
-      <c r="J44" s="67" t="s">
+      <c r="J44" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="K44" s="86" t="s">
+      <c r="K44" s="64" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:11" s="37" customFormat="1" ht="38" x14ac:dyDescent="0.2">
-      <c r="A45" s="44"/>
-      <c r="B45" s="44"/>
-      <c r="C45" s="44"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="49">
+    <row r="45" spans="1:11" s="15" customFormat="1" ht="38" x14ac:dyDescent="0.2">
+      <c r="A45" s="22"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="27">
         <v>44</v>
       </c>
-      <c r="F45" s="65" t="s">
+      <c r="F45" s="43" t="s">
         <v>205</v>
       </c>
-      <c r="G45" s="66">
+      <c r="G45" s="44">
         <v>2</v>
       </c>
-      <c r="H45" s="67" t="s">
+      <c r="H45" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="I45" s="87" t="s">
+      <c r="I45" s="65" t="s">
         <v>207</v>
       </c>
-      <c r="J45" s="67" t="s">
+      <c r="J45" s="45" t="s">
         <v>208</v>
       </c>
-      <c r="K45" s="68" t="s">
+      <c r="K45" s="46" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="46" spans="1:11" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.2">
-      <c r="A46" s="44"/>
-      <c r="B46" s="44"/>
-      <c r="C46" s="44"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="49">
+    <row r="46" spans="1:11" s="15" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+      <c r="A46" s="22"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="27">
         <v>45</v>
       </c>
-      <c r="F46" s="65" t="s">
+      <c r="F46" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="G46" s="66">
+      <c r="G46" s="44">
         <v>2</v>
       </c>
-      <c r="H46" s="67" t="s">
+      <c r="H46" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="I46" s="87" t="s">
+      <c r="I46" s="65" t="s">
         <v>212</v>
       </c>
-      <c r="J46" s="67" t="s">
+      <c r="J46" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="K46" s="68" t="s">
+      <c r="K46" s="46" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="47" spans="1:11" s="37" customFormat="1" ht="38" x14ac:dyDescent="0.2">
-      <c r="A47" s="45"/>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="49">
+    <row r="47" spans="1:11" s="15" customFormat="1" ht="38" x14ac:dyDescent="0.2">
+      <c r="A47" s="23"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="27">
         <v>46</v>
       </c>
-      <c r="F47" s="64" t="s">
+      <c r="F47" s="42" t="s">
         <v>215</v>
       </c>
-      <c r="G47" s="69">
+      <c r="G47" s="47">
         <v>1</v>
       </c>
-      <c r="H47" s="84" t="s">
+      <c r="H47" s="62" t="s">
         <v>216</v>
       </c>
-      <c r="I47" s="63" t="s">
+      <c r="I47" s="41" t="s">
         <v>217</v>
       </c>
-      <c r="J47" s="63" t="s">
+      <c r="J47" s="41" t="s">
         <v>218</v>
       </c>
-      <c r="K47" s="70" t="s">
+      <c r="K47" s="48" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="48" spans="1:11" s="37" customFormat="1" ht="19" x14ac:dyDescent="0.2">
-      <c r="A48" s="45"/>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="49">
+    <row r="48" spans="1:11" s="15" customFormat="1" ht="19" x14ac:dyDescent="0.2">
+      <c r="A48" s="23"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="27">
         <v>47</v>
       </c>
-      <c r="F48" s="64" t="s">
+      <c r="F48" s="42" t="s">
         <v>220</v>
       </c>
-      <c r="G48" s="69">
+      <c r="G48" s="47">
         <v>1</v>
       </c>
-      <c r="H48" s="84" t="s">
+      <c r="H48" s="62" t="s">
         <v>221</v>
       </c>
-      <c r="I48" s="63" t="s">
+      <c r="I48" s="41" t="s">
         <v>222</v>
       </c>
-      <c r="J48" s="63" t="s">
+      <c r="J48" s="41" t="s">
         <v>223</v>
       </c>
-      <c r="K48" s="71" t="s">
+      <c r="K48" s="49" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="49" spans="1:11" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.2">
-      <c r="A49" s="45"/>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="49">
+    <row r="49" spans="1:11" s="15" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+      <c r="A49" s="23"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="27">
         <v>48</v>
       </c>
-      <c r="F49" s="65" t="s">
+      <c r="F49" s="43" t="s">
         <v>225</v>
       </c>
-      <c r="G49" s="66">
+      <c r="G49" s="44">
         <v>4</v>
       </c>
-      <c r="H49" s="67" t="s">
+      <c r="H49" s="45" t="s">
         <v>226</v>
       </c>
-      <c r="I49" s="67" t="s">
+      <c r="I49" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="J49" s="67" t="s">
+      <c r="J49" s="45" t="s">
         <v>228</v>
       </c>
-      <c r="K49" s="86" t="s">
+      <c r="K49" s="64" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="50" spans="1:11" s="37" customFormat="1" ht="76" x14ac:dyDescent="0.2">
-      <c r="A50" s="45"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="49">
+    <row r="50" spans="1:11" s="15" customFormat="1" ht="76" x14ac:dyDescent="0.2">
+      <c r="A50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
+      <c r="D50" s="23"/>
+      <c r="E50" s="27">
         <v>49</v>
       </c>
-      <c r="F50" s="65" t="s">
+      <c r="F50" s="43" t="s">
         <v>230</v>
       </c>
-      <c r="G50" s="66">
+      <c r="G50" s="44">
         <v>4</v>
       </c>
-      <c r="H50" s="67" t="s">
+      <c r="H50" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="I50" s="67" t="s">
+      <c r="I50" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="J50" s="67" t="s">
+      <c r="J50" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="K50" s="86" t="s">
+      <c r="K50" s="64" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="51" spans="1:11" s="37" customFormat="1" ht="38" x14ac:dyDescent="0.2">
-      <c r="A51" s="45"/>
-      <c r="B51" s="45"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="49">
+    <row r="51" spans="1:11" s="15" customFormat="1" ht="38" x14ac:dyDescent="0.2">
+      <c r="A51" s="23"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="23"/>
+      <c r="E51" s="27">
         <v>50</v>
       </c>
-      <c r="F51" s="65" t="s">
+      <c r="F51" s="43" t="s">
         <v>235</v>
       </c>
-      <c r="G51" s="66">
+      <c r="G51" s="44">
         <v>3</v>
       </c>
-      <c r="H51" s="67" t="s">
+      <c r="H51" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="I51" s="67" t="s">
+      <c r="I51" s="45" t="s">
         <v>237</v>
       </c>
-      <c r="J51" s="87" t="s">
+      <c r="J51" s="65" t="s">
         <v>238</v>
       </c>
-      <c r="K51" s="68" t="s">
+      <c r="K51" s="46" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="52" spans="1:11" s="37" customFormat="1" ht="95" x14ac:dyDescent="0.2">
-      <c r="A52" s="45"/>
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="49">
+    <row r="52" spans="1:11" s="15" customFormat="1" ht="95" x14ac:dyDescent="0.2">
+      <c r="A52" s="23"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="23"/>
+      <c r="E52" s="27">
         <v>51</v>
       </c>
-      <c r="F52" s="65" t="s">
+      <c r="F52" s="43" t="s">
         <v>240</v>
       </c>
-      <c r="G52" s="66">
+      <c r="G52" s="44">
         <v>4</v>
       </c>
-      <c r="H52" s="67" t="s">
+      <c r="H52" s="45" t="s">
         <v>241</v>
       </c>
-      <c r="I52" s="67" t="s">
+      <c r="I52" s="45" t="s">
         <v>242</v>
       </c>
-      <c r="J52" s="67" t="s">
+      <c r="J52" s="45" t="s">
         <v>243</v>
       </c>
-      <c r="K52" s="88" t="s">
+      <c r="K52" s="66" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="53" spans="1:11" s="37" customFormat="1" ht="76" x14ac:dyDescent="0.2">
-      <c r="A53" s="45"/>
-      <c r="B53" s="45"/>
-      <c r="C53" s="45"/>
-      <c r="D53" s="45"/>
-      <c r="E53" s="49">
+    <row r="53" spans="1:11" s="15" customFormat="1" ht="76" x14ac:dyDescent="0.2">
+      <c r="A53" s="23"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
+      <c r="D53" s="23"/>
+      <c r="E53" s="27">
         <v>52</v>
       </c>
-      <c r="F53" s="65" t="s">
+      <c r="F53" s="43" t="s">
         <v>245</v>
       </c>
-      <c r="G53" s="66">
+      <c r="G53" s="44">
         <v>4</v>
       </c>
-      <c r="H53" s="67" t="s">
+      <c r="H53" s="45" t="s">
         <v>246</v>
       </c>
-      <c r="I53" s="67" t="s">
+      <c r="I53" s="45" t="s">
         <v>247</v>
       </c>
-      <c r="J53" s="67" t="s">
+      <c r="J53" s="45" t="s">
         <v>248</v>
       </c>
-      <c r="K53" s="88" t="s">
+      <c r="K53" s="66" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="37" customFormat="1" ht="76" x14ac:dyDescent="0.2">
-      <c r="A54" s="45"/>
-      <c r="B54" s="45"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="49">
+    <row r="54" spans="1:11" s="15" customFormat="1" ht="76" x14ac:dyDescent="0.2">
+      <c r="A54" s="23"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="27">
         <v>53</v>
       </c>
-      <c r="F54" s="65" t="s">
+      <c r="F54" s="43" t="s">
         <v>250</v>
       </c>
-      <c r="G54" s="66">
+      <c r="G54" s="44">
         <v>3</v>
       </c>
-      <c r="H54" s="67" t="s">
+      <c r="H54" s="45" t="s">
         <v>251</v>
       </c>
-      <c r="I54" s="67" t="s">
+      <c r="I54" s="45" t="s">
         <v>252</v>
       </c>
-      <c r="J54" s="87" t="s">
+      <c r="J54" s="65" t="s">
         <v>253</v>
       </c>
-      <c r="K54" s="68" t="s">
+      <c r="K54" s="46" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="37" customFormat="1" ht="76" x14ac:dyDescent="0.2">
-      <c r="A55" s="45"/>
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="49">
+    <row r="55" spans="1:11" s="15" customFormat="1" ht="76" x14ac:dyDescent="0.2">
+      <c r="A55" s="23"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="27">
         <v>54</v>
       </c>
-      <c r="F55" s="64" t="s">
+      <c r="F55" s="42" t="s">
         <v>255</v>
       </c>
-      <c r="G55" s="69">
+      <c r="G55" s="47">
         <v>1</v>
       </c>
-      <c r="H55" s="84" t="s">
+      <c r="H55" s="62" t="s">
         <v>256</v>
       </c>
-      <c r="I55" s="63" t="s">
+      <c r="I55" s="41" t="s">
         <v>257</v>
       </c>
-      <c r="J55" s="63" t="s">
+      <c r="J55" s="41" t="s">
         <v>258</v>
       </c>
-      <c r="K55" s="71" t="s">
+      <c r="K55" s="49" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="37" customFormat="1" ht="38" x14ac:dyDescent="0.2">
-      <c r="A56" s="45"/>
-      <c r="B56" s="45"/>
-      <c r="C56" s="45"/>
-      <c r="D56" s="45"/>
-      <c r="E56" s="49">
+    <row r="56" spans="1:11" s="15" customFormat="1" ht="38" x14ac:dyDescent="0.2">
+      <c r="A56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="27">
         <v>55</v>
       </c>
-      <c r="F56" s="72" t="s">
+      <c r="F56" s="50" t="s">
         <v>260</v>
       </c>
-      <c r="G56" s="56">
+      <c r="G56" s="34">
         <v>1</v>
       </c>
-      <c r="H56" s="82" t="s">
+      <c r="H56" s="60" t="s">
         <v>261</v>
       </c>
-      <c r="I56" s="57" t="s">
+      <c r="I56" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="J56" s="57" t="s">
+      <c r="J56" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="K56" s="73" t="s">
+      <c r="K56" s="51" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="57" spans="1:11" s="37" customFormat="1" ht="57" x14ac:dyDescent="0.2">
-      <c r="A57" s="45"/>
-      <c r="B57" s="45"/>
-      <c r="C57" s="45"/>
-      <c r="D57" s="45"/>
-      <c r="E57" s="49">
+    <row r="57" spans="1:11" s="15" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+      <c r="A57" s="23"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
+      <c r="D57" s="23"/>
+      <c r="E57" s="27">
         <v>56</v>
       </c>
-      <c r="F57" s="74" t="s">
+      <c r="F57" s="52" t="s">
         <v>265</v>
       </c>
-      <c r="G57" s="75">
+      <c r="G57" s="53">
         <v>2</v>
       </c>
-      <c r="H57" s="76" t="s">
+      <c r="H57" s="54" t="s">
         <v>266</v>
       </c>
-      <c r="I57" s="89" t="s">
+      <c r="I57" s="67" t="s">
         <v>267</v>
       </c>
-      <c r="J57" s="76" t="s">
+      <c r="J57" s="54" t="s">
         <v>268</v>
       </c>
-      <c r="K57" s="76" t="s">
+      <c r="K57" s="54" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="58" spans="1:11" s="30" customFormat="1" ht="76" x14ac:dyDescent="0.15">
-      <c r="A58" s="33"/>
-      <c r="B58" s="33"/>
-      <c r="C58" s="33"/>
-      <c r="D58" s="34"/>
-      <c r="E58" s="49">
+    <row r="58" spans="1:11" s="8" customFormat="1" ht="76" x14ac:dyDescent="0.15">
+      <c r="A58" s="11"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="27">
         <v>57</v>
       </c>
-      <c r="F58" s="49" t="s">
+      <c r="F58" s="27" t="s">
         <v>270</v>
       </c>
-      <c r="G58" s="49">
+      <c r="G58" s="27">
         <v>1</v>
       </c>
-      <c r="H58" s="80" t="s">
+      <c r="H58" s="58" t="s">
         <v>271</v>
       </c>
-      <c r="I58" s="51" t="s">
+      <c r="I58" s="29" t="s">
         <v>272</v>
       </c>
-      <c r="J58" s="51" t="s">
+      <c r="J58" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="K58" s="51" t="s">
+      <c r="K58" s="29" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="30" customFormat="1" ht="76" x14ac:dyDescent="0.15">
-      <c r="A59" s="33"/>
-      <c r="B59" s="33"/>
-      <c r="C59" s="33"/>
-      <c r="D59" s="34"/>
-      <c r="E59" s="49">
+    <row r="59" spans="1:11" s="8" customFormat="1" ht="76" x14ac:dyDescent="0.15">
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="27">
         <v>58</v>
       </c>
-      <c r="F59" s="49" t="s">
+      <c r="F59" s="27" t="s">
         <v>275</v>
       </c>
-      <c r="G59" s="49">
+      <c r="G59" s="27">
         <v>1</v>
       </c>
-      <c r="H59" s="80" t="s">
+      <c r="H59" s="58" t="s">
         <v>276</v>
       </c>
-      <c r="I59" s="51" t="s">
+      <c r="I59" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="J59" s="51" t="s">
+      <c r="J59" s="29" t="s">
         <v>278</v>
       </c>
-      <c r="K59" s="51" t="s">
+      <c r="K59" s="29" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="60" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="A60" s="33"/>
-      <c r="B60" s="35"/>
-      <c r="C60" s="35"/>
-      <c r="D60" s="36"/>
-      <c r="E60" s="49">
+    <row r="60" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="A60" s="11"/>
+      <c r="B60" s="13"/>
+      <c r="C60" s="13"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="27">
         <v>59</v>
       </c>
-      <c r="F60" s="49" t="s">
+      <c r="F60" s="27" t="s">
         <v>280</v>
       </c>
-      <c r="G60" s="49">
+      <c r="G60" s="27">
         <v>1</v>
       </c>
-      <c r="H60" s="80" t="s">
+      <c r="H60" s="58" t="s">
         <v>281</v>
       </c>
-      <c r="I60" s="51" t="s">
+      <c r="I60" s="29" t="s">
         <v>282</v>
       </c>
-      <c r="J60" s="51" t="s">
+      <c r="J60" s="29" t="s">
         <v>283</v>
       </c>
-      <c r="K60" s="51" t="s">
+      <c r="K60" s="29" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="61" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="A61" s="33"/>
-      <c r="B61" s="35"/>
-      <c r="C61" s="35"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="49">
+    <row r="61" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="A61" s="11"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="14"/>
+      <c r="E61" s="27">
         <v>60</v>
       </c>
-      <c r="F61" s="49" t="s">
+      <c r="F61" s="27" t="s">
         <v>285</v>
       </c>
-      <c r="G61" s="49">
+      <c r="G61" s="27">
         <v>1</v>
       </c>
-      <c r="H61" s="80" t="s">
+      <c r="H61" s="58" t="s">
         <v>286</v>
       </c>
-      <c r="I61" s="51" t="s">
+      <c r="I61" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="J61" s="51" t="s">
+      <c r="J61" s="29" t="s">
         <v>288</v>
       </c>
-      <c r="K61" s="51" t="s">
+      <c r="K61" s="29" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="62" spans="1:11" s="30" customFormat="1" ht="95" x14ac:dyDescent="0.15">
-      <c r="A62" s="33"/>
-      <c r="B62" s="35"/>
-      <c r="C62" s="35"/>
-      <c r="D62" s="36"/>
-      <c r="E62" s="49">
+    <row r="62" spans="1:11" s="8" customFormat="1" ht="95" x14ac:dyDescent="0.15">
+      <c r="A62" s="11"/>
+      <c r="B62" s="13"/>
+      <c r="C62" s="13"/>
+      <c r="D62" s="14"/>
+      <c r="E62" s="27">
         <v>61</v>
       </c>
-      <c r="F62" s="49" t="s">
+      <c r="F62" s="27" t="s">
         <v>290</v>
       </c>
-      <c r="G62" s="49">
+      <c r="G62" s="27">
         <v>1</v>
       </c>
-      <c r="H62" s="80" t="s">
+      <c r="H62" s="58" t="s">
         <v>291</v>
       </c>
-      <c r="I62" s="51" t="s">
+      <c r="I62" s="29" t="s">
         <v>292</v>
       </c>
-      <c r="J62" s="51" t="s">
+      <c r="J62" s="29" t="s">
         <v>293</v>
       </c>
-      <c r="K62" s="51" t="s">
+      <c r="K62" s="29" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="63" spans="1:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E63" s="49">
+    <row r="63" spans="1:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E63" s="27">
         <v>62</v>
       </c>
-      <c r="F63" s="49" t="s">
+      <c r="F63" s="27" t="s">
         <v>295</v>
       </c>
-      <c r="G63" s="49">
+      <c r="G63" s="27">
         <v>1</v>
       </c>
-      <c r="H63" s="80" t="s">
+      <c r="H63" s="58" t="s">
         <v>296</v>
       </c>
-      <c r="I63" s="51" t="s">
+      <c r="I63" s="29" t="s">
         <v>297</v>
       </c>
-      <c r="J63" s="51" t="s">
+      <c r="J63" s="29" t="s">
         <v>298</v>
       </c>
-      <c r="K63" s="51" t="s">
+      <c r="K63" s="29" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="64" spans="1:11" s="30" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E64" s="49">
+    <row r="64" spans="1:11" s="8" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E64" s="27">
         <v>63</v>
       </c>
-      <c r="F64" s="49" t="s">
+      <c r="F64" s="27" t="s">
         <v>300</v>
       </c>
-      <c r="G64" s="49">
+      <c r="G64" s="27">
         <v>1</v>
       </c>
-      <c r="H64" s="80" t="s">
+      <c r="H64" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="I64" s="51" t="s">
+      <c r="I64" s="29" t="s">
         <v>302</v>
       </c>
-      <c r="J64" s="51" t="s">
+      <c r="J64" s="29" t="s">
         <v>303</v>
       </c>
-      <c r="K64" s="51" t="s">
+      <c r="K64" s="29" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="65" spans="5:11" s="30" customFormat="1" ht="76" x14ac:dyDescent="0.15">
-      <c r="E65" s="49">
+    <row r="65" spans="5:11" s="8" customFormat="1" ht="76" x14ac:dyDescent="0.15">
+      <c r="E65" s="27">
         <v>64</v>
       </c>
-      <c r="F65" s="49" t="s">
+      <c r="F65" s="27" t="s">
         <v>305</v>
       </c>
-      <c r="G65" s="49">
+      <c r="G65" s="27">
         <v>1</v>
       </c>
-      <c r="H65" s="80" t="s">
+      <c r="H65" s="58" t="s">
         <v>306</v>
       </c>
-      <c r="I65" s="51" t="s">
+      <c r="I65" s="29" t="s">
         <v>307</v>
       </c>
-      <c r="J65" s="51" t="s">
+      <c r="J65" s="29" t="s">
         <v>308</v>
       </c>
-      <c r="K65" s="51" t="s">
+      <c r="K65" s="29" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="66" spans="5:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E66" s="49">
+    <row r="66" spans="5:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E66" s="27">
         <v>65</v>
       </c>
-      <c r="F66" s="49" t="s">
+      <c r="F66" s="27" t="s">
         <v>310</v>
       </c>
-      <c r="G66" s="49">
+      <c r="G66" s="27">
         <v>1</v>
       </c>
-      <c r="H66" s="80" t="s">
+      <c r="H66" s="58" t="s">
         <v>311</v>
       </c>
-      <c r="I66" s="51" t="s">
+      <c r="I66" s="29" t="s">
         <v>312</v>
       </c>
-      <c r="J66" s="51" t="s">
+      <c r="J66" s="29" t="s">
         <v>313</v>
       </c>
-      <c r="K66" s="51" t="s">
+      <c r="K66" s="29" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="67" spans="5:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E67" s="49">
+    <row r="67" spans="5:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E67" s="27">
         <v>66</v>
       </c>
-      <c r="F67" s="49" t="s">
+      <c r="F67" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G67" s="49">
+      <c r="G67" s="27">
         <v>1</v>
       </c>
-      <c r="H67" s="80" t="s">
+      <c r="H67" s="58" t="s">
         <v>316</v>
       </c>
-      <c r="I67" s="51" t="s">
+      <c r="I67" s="29" t="s">
         <v>317</v>
       </c>
-      <c r="J67" s="51" t="s">
+      <c r="J67" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="K67" s="51" t="s">
+      <c r="K67" s="29" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="68" spans="5:11" s="30" customFormat="1" ht="76" x14ac:dyDescent="0.15">
-      <c r="E68" s="49">
+    <row r="68" spans="5:11" s="8" customFormat="1" ht="76" x14ac:dyDescent="0.15">
+      <c r="E68" s="27">
         <v>67</v>
       </c>
-      <c r="F68" s="49" t="s">
+      <c r="F68" s="27" t="s">
         <v>320</v>
       </c>
-      <c r="G68" s="49">
+      <c r="G68" s="27">
         <v>1</v>
       </c>
-      <c r="H68" s="80" t="s">
+      <c r="H68" s="58" t="s">
         <v>321</v>
       </c>
-      <c r="I68" s="51" t="s">
+      <c r="I68" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="J68" s="51" t="s">
+      <c r="J68" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="K68" s="51" t="s">
+      <c r="K68" s="29" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="5:11" s="30" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E69" s="49">
+    <row r="69" spans="5:11" s="8" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E69" s="27">
         <v>68</v>
       </c>
-      <c r="F69" s="49" t="s">
+      <c r="F69" s="27" t="s">
         <v>320</v>
       </c>
-      <c r="G69" s="49">
+      <c r="G69" s="27">
         <v>1</v>
       </c>
-      <c r="H69" s="80" t="s">
+      <c r="H69" s="58" t="s">
         <v>321</v>
       </c>
-      <c r="I69" s="51" t="s">
+      <c r="I69" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="J69" s="51" t="s">
+      <c r="J69" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="K69" s="51" t="s">
+      <c r="K69" s="29" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="70" spans="5:11" s="30" customFormat="1" ht="76" x14ac:dyDescent="0.15">
-      <c r="E70" s="49">
+    <row r="70" spans="5:11" s="8" customFormat="1" ht="76" x14ac:dyDescent="0.15">
+      <c r="E70" s="27">
         <v>69</v>
       </c>
-      <c r="F70" s="49" t="s">
+      <c r="F70" s="27" t="s">
         <v>325</v>
       </c>
-      <c r="G70" s="49">
+      <c r="G70" s="27">
         <v>1</v>
       </c>
-      <c r="H70" s="80" t="s">
+      <c r="H70" s="58" t="s">
         <v>326</v>
       </c>
-      <c r="I70" s="51" t="s">
+      <c r="I70" s="29" t="s">
         <v>327</v>
       </c>
-      <c r="J70" s="51" t="s">
+      <c r="J70" s="29" t="s">
         <v>279</v>
       </c>
-      <c r="K70" s="51" t="s">
+      <c r="K70" s="29" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="71" spans="5:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E71" s="49">
+    <row r="71" spans="5:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E71" s="27">
         <v>70</v>
       </c>
-      <c r="F71" s="49" t="s">
+      <c r="F71" s="27" t="s">
         <v>329</v>
       </c>
-      <c r="G71" s="49">
+      <c r="G71" s="27">
         <v>1</v>
       </c>
-      <c r="H71" s="80" t="s">
+      <c r="H71" s="58" t="s">
         <v>330</v>
       </c>
-      <c r="I71" s="51" t="s">
+      <c r="I71" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="J71" s="51" t="s">
+      <c r="J71" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="K71" s="51" t="s">
+      <c r="K71" s="29" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="72" spans="5:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E72" s="49">
+    <row r="72" spans="5:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E72" s="27">
         <v>71</v>
       </c>
-      <c r="F72" s="49" t="s">
+      <c r="F72" s="27" t="s">
         <v>334</v>
       </c>
-      <c r="G72" s="49">
+      <c r="G72" s="27">
         <v>1</v>
       </c>
-      <c r="H72" s="80" t="s">
+      <c r="H72" s="58" t="s">
         <v>331</v>
       </c>
-      <c r="I72" s="51" t="s">
+      <c r="I72" s="29" t="s">
         <v>330</v>
       </c>
-      <c r="J72" s="51" t="s">
+      <c r="J72" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="K72" s="51" t="s">
+      <c r="K72" s="29" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="73" spans="5:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E73" s="49">
+    <row r="73" spans="5:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E73" s="27">
         <v>72</v>
       </c>
-      <c r="F73" s="49" t="s">
+      <c r="F73" s="27" t="s">
         <v>335</v>
       </c>
-      <c r="G73" s="49">
+      <c r="G73" s="27">
         <v>3</v>
       </c>
-      <c r="H73" s="51" t="s">
+      <c r="H73" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="I73" s="51" t="s">
+      <c r="I73" s="29" t="s">
         <v>332</v>
       </c>
-      <c r="J73" s="80" t="s">
+      <c r="J73" s="58" t="s">
         <v>333</v>
       </c>
-      <c r="K73" s="51" t="s">
+      <c r="K73" s="29" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="74" spans="5:11" s="30" customFormat="1" ht="76" x14ac:dyDescent="0.15">
-      <c r="E74" s="49">
+    <row r="74" spans="5:11" s="8" customFormat="1" ht="76" x14ac:dyDescent="0.15">
+      <c r="E74" s="27">
         <v>73</v>
       </c>
-      <c r="F74" s="49" t="s">
+      <c r="F74" s="27" t="s">
         <v>336</v>
       </c>
-      <c r="G74" s="49">
+      <c r="G74" s="27">
         <v>1</v>
       </c>
-      <c r="H74" s="80" t="s">
+      <c r="H74" s="58" t="s">
         <v>337</v>
       </c>
-      <c r="I74" s="51" t="s">
+      <c r="I74" s="29" t="s">
         <v>338</v>
       </c>
-      <c r="J74" s="51" t="s">
+      <c r="J74" s="29" t="s">
         <v>339</v>
       </c>
-      <c r="K74" s="51" t="s">
+      <c r="K74" s="29" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="75" spans="5:11" s="30" customFormat="1" ht="133" x14ac:dyDescent="0.15">
-      <c r="E75" s="49">
+    <row r="75" spans="5:11" s="8" customFormat="1" ht="133" x14ac:dyDescent="0.15">
+      <c r="E75" s="27">
         <v>74</v>
       </c>
-      <c r="F75" s="49" t="s">
+      <c r="F75" s="27" t="s">
         <v>341</v>
       </c>
-      <c r="G75" s="49">
+      <c r="G75" s="27">
         <v>1</v>
       </c>
-      <c r="H75" s="80" t="s">
+      <c r="H75" s="58" t="s">
         <v>342</v>
       </c>
-      <c r="I75" s="51" t="s">
+      <c r="I75" s="29" t="s">
         <v>343</v>
       </c>
-      <c r="J75" s="51" t="s">
+      <c r="J75" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="K75" s="51" t="s">
+      <c r="K75" s="29" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="76" spans="5:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E76" s="49">
+    <row r="76" spans="5:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E76" s="27">
         <v>75</v>
       </c>
-      <c r="F76" s="49" t="s">
+      <c r="F76" s="27" t="s">
         <v>346</v>
       </c>
-      <c r="G76" s="49">
+      <c r="G76" s="27">
         <v>4</v>
       </c>
-      <c r="H76" s="51" t="s">
+      <c r="H76" s="29" t="s">
         <v>347</v>
       </c>
-      <c r="I76" s="51" t="s">
+      <c r="I76" s="29" t="s">
         <v>348</v>
       </c>
-      <c r="J76" s="51" t="s">
+      <c r="J76" s="29" t="s">
         <v>349</v>
       </c>
-      <c r="K76" s="80" t="s">
+      <c r="K76" s="58" t="s">
         <v>350</v>
       </c>
     </row>
-    <row r="77" spans="5:11" s="30" customFormat="1" ht="72.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E77" s="49">
+    <row r="77" spans="5:11" s="8" customFormat="1" ht="72.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E77" s="27">
         <v>76</v>
       </c>
-      <c r="F77" s="49" t="s">
+      <c r="F77" s="27" t="s">
         <v>351</v>
       </c>
-      <c r="G77" s="49">
+      <c r="G77" s="27">
         <v>4</v>
       </c>
-      <c r="H77" s="51" t="s">
+      <c r="H77" s="29" t="s">
         <v>352</v>
       </c>
-      <c r="I77" s="51" t="s">
+      <c r="I77" s="29" t="s">
         <v>353</v>
       </c>
-      <c r="J77" s="51" t="s">
+      <c r="J77" s="29" t="s">
         <v>354</v>
       </c>
-      <c r="K77" s="80" t="s">
+      <c r="K77" s="58" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="78" spans="5:11" s="30" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E78" s="49">
+    <row r="78" spans="5:11" s="8" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E78" s="27">
         <v>77</v>
       </c>
-      <c r="F78" s="49" t="s">
+      <c r="F78" s="27" t="s">
         <v>356</v>
       </c>
-      <c r="G78" s="49">
+      <c r="G78" s="27">
         <v>4</v>
       </c>
-      <c r="H78" s="51" t="s">
+      <c r="H78" s="29" t="s">
         <v>357</v>
       </c>
-      <c r="I78" s="51" t="s">
+      <c r="I78" s="29" t="s">
         <v>358</v>
       </c>
-      <c r="J78" s="51" t="s">
+      <c r="J78" s="29" t="s">
         <v>359</v>
       </c>
-      <c r="K78" s="80" t="s">
+      <c r="K78" s="58" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="79" spans="5:11" s="30" customFormat="1" ht="133" x14ac:dyDescent="0.15">
-      <c r="E79" s="49">
+    <row r="79" spans="5:11" s="8" customFormat="1" ht="133" x14ac:dyDescent="0.15">
+      <c r="E79" s="27">
         <v>78</v>
       </c>
-      <c r="F79" s="49" t="s">
+      <c r="F79" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="G79" s="49">
+      <c r="G79" s="27">
         <v>1</v>
       </c>
-      <c r="H79" s="80" t="s">
+      <c r="H79" s="58" t="s">
         <v>362</v>
       </c>
-      <c r="I79" s="51" t="s">
+      <c r="I79" s="29" t="s">
         <v>363</v>
       </c>
-      <c r="J79" s="51" t="s">
+      <c r="J79" s="29" t="s">
         <v>364</v>
       </c>
-      <c r="K79" s="51" t="s">
+      <c r="K79" s="29" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="80" spans="5:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E80" s="49">
+    <row r="80" spans="5:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E80" s="27">
         <v>79</v>
       </c>
-      <c r="F80" s="49" t="s">
+      <c r="F80" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="G80" s="49">
+      <c r="G80" s="27">
         <v>1</v>
       </c>
-      <c r="H80" s="80" t="s">
+      <c r="H80" s="58" t="s">
         <v>367</v>
       </c>
-      <c r="I80" s="51" t="s">
+      <c r="I80" s="29" t="s">
         <v>368</v>
       </c>
-      <c r="J80" s="51" t="s">
+      <c r="J80" s="29" t="s">
         <v>369</v>
       </c>
-      <c r="K80" s="51" t="s">
+      <c r="K80" s="29" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="81" spans="5:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E81" s="49">
+    <row r="81" spans="5:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E81" s="27">
         <v>80</v>
       </c>
-      <c r="F81" s="49" t="s">
+      <c r="F81" s="27" t="s">
         <v>371</v>
       </c>
-      <c r="G81" s="49">
+      <c r="G81" s="27">
         <v>1</v>
       </c>
-      <c r="H81" s="80" t="s">
+      <c r="H81" s="58" t="s">
         <v>372</v>
       </c>
-      <c r="I81" s="51" t="s">
+      <c r="I81" s="29" t="s">
         <v>373</v>
       </c>
-      <c r="J81" s="51" t="s">
+      <c r="J81" s="29" t="s">
         <v>374</v>
       </c>
-      <c r="K81" s="51" t="s">
+      <c r="K81" s="29" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="82" spans="5:11" s="30" customFormat="1" ht="133" x14ac:dyDescent="0.15">
-      <c r="E82" s="49">
+    <row r="82" spans="5:11" s="8" customFormat="1" ht="133" x14ac:dyDescent="0.15">
+      <c r="E82" s="27">
         <v>81</v>
       </c>
-      <c r="F82" s="49" t="s">
+      <c r="F82" s="27" t="s">
         <v>376</v>
       </c>
-      <c r="G82" s="49">
+      <c r="G82" s="27">
         <v>1</v>
       </c>
-      <c r="H82" s="80" t="s">
+      <c r="H82" s="58" t="s">
         <v>377</v>
       </c>
-      <c r="I82" s="51" t="s">
+      <c r="I82" s="29" t="s">
         <v>378</v>
       </c>
-      <c r="J82" s="51" t="s">
+      <c r="J82" s="29" t="s">
         <v>379</v>
       </c>
-      <c r="K82" s="51" t="s">
+      <c r="K82" s="29" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="83" spans="5:11" s="30" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E83" s="49">
+    <row r="83" spans="5:11" s="8" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E83" s="27">
         <v>82</v>
       </c>
-      <c r="F83" s="49" t="s">
+      <c r="F83" s="27" t="s">
         <v>381</v>
       </c>
-      <c r="G83" s="49">
+      <c r="G83" s="27">
         <v>1</v>
       </c>
-      <c r="H83" s="80" t="s">
+      <c r="H83" s="58" t="s">
         <v>382</v>
       </c>
-      <c r="I83" s="51" t="s">
+      <c r="I83" s="29" t="s">
         <v>383</v>
       </c>
-      <c r="J83" s="51" t="s">
+      <c r="J83" s="29" t="s">
         <v>384</v>
       </c>
-      <c r="K83" s="51" t="s">
+      <c r="K83" s="29" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="84" spans="5:11" s="30" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E84" s="49">
+    <row r="84" spans="5:11" s="8" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E84" s="27">
         <v>83</v>
       </c>
-      <c r="F84" s="49" t="s">
+      <c r="F84" s="27" t="s">
         <v>386</v>
       </c>
-      <c r="G84" s="49">
+      <c r="G84" s="27">
         <v>1</v>
       </c>
-      <c r="H84" s="80" t="s">
+      <c r="H84" s="58" t="s">
         <v>387</v>
       </c>
-      <c r="I84" s="51" t="s">
+      <c r="I84" s="29" t="s">
         <v>388</v>
       </c>
-      <c r="J84" s="51" t="s">
+      <c r="J84" s="29" t="s">
         <v>389</v>
       </c>
-      <c r="K84" s="51" t="s">
+      <c r="K84" s="29" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="85" spans="5:11" s="30" customFormat="1" ht="57.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E85" s="49">
+    <row r="85" spans="5:11" s="8" customFormat="1" ht="57.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E85" s="27">
         <v>84</v>
       </c>
-      <c r="F85" s="49" t="s">
+      <c r="F85" s="27" t="s">
         <v>315</v>
       </c>
-      <c r="G85" s="49">
+      <c r="G85" s="27">
         <v>1</v>
       </c>
-      <c r="H85" s="80" t="s">
+      <c r="H85" s="58" t="s">
         <v>391</v>
       </c>
-      <c r="I85" s="51" t="s">
+      <c r="I85" s="29" t="s">
         <v>392</v>
       </c>
-      <c r="J85" s="51" t="s">
+      <c r="J85" s="29" t="s">
         <v>393</v>
       </c>
-      <c r="K85" s="51" t="s">
+      <c r="K85" s="29" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="86" spans="5:11" s="38" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="E86" s="77">
+    <row r="86" spans="5:11" s="16" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E86" s="55">
         <v>85</v>
       </c>
-      <c r="F86" s="77" t="s">
+      <c r="F86" s="55" t="s">
         <v>395</v>
       </c>
-      <c r="G86" s="77">
+      <c r="G86" s="55">
         <v>3</v>
       </c>
-      <c r="H86" s="78" t="s">
+      <c r="H86" s="56" t="s">
         <v>396</v>
       </c>
-      <c r="I86" s="78" t="s">
+      <c r="I86" s="56" t="s">
         <v>397</v>
       </c>
-      <c r="J86" s="90" t="s">
+      <c r="J86" s="68" t="s">
         <v>398</v>
       </c>
-      <c r="K86" s="78" t="s">
+      <c r="K86" s="56" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="87" spans="5:11" s="30" customFormat="1" ht="133" x14ac:dyDescent="0.15">
-      <c r="E87" s="49">
+    <row r="87" spans="5:11" s="8" customFormat="1" ht="133" x14ac:dyDescent="0.15">
+      <c r="E87" s="27">
         <v>86</v>
       </c>
-      <c r="F87" s="49" t="s">
+      <c r="F87" s="27" t="s">
         <v>400</v>
       </c>
-      <c r="G87" s="49">
+      <c r="G87" s="27">
         <v>1</v>
       </c>
-      <c r="H87" s="80" t="s">
+      <c r="H87" s="58" t="s">
         <v>401</v>
       </c>
-      <c r="I87" s="51" t="s">
+      <c r="I87" s="29" t="s">
         <v>402</v>
       </c>
-      <c r="J87" s="51" t="s">
+      <c r="J87" s="29" t="s">
         <v>403</v>
       </c>
-      <c r="K87" s="51" t="s">
+      <c r="K87" s="29" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="88" spans="5:11" s="30" customFormat="1" ht="114" x14ac:dyDescent="0.15">
-      <c r="E88" s="49">
+    <row r="88" spans="5:11" s="8" customFormat="1" ht="114" x14ac:dyDescent="0.15">
+      <c r="E88" s="27">
         <v>87</v>
       </c>
-      <c r="F88" s="49" t="s">
+      <c r="F88" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="G88" s="49">
+      <c r="G88" s="27">
         <v>1</v>
       </c>
-      <c r="H88" s="80" t="s">
+      <c r="H88" s="58" t="s">
         <v>406</v>
       </c>
-      <c r="I88" s="51" t="s">
+      <c r="I88" s="29" t="s">
         <v>407</v>
       </c>
-      <c r="J88" s="51" t="s">
+      <c r="J88" s="29" t="s">
         <v>408</v>
       </c>
-      <c r="K88" s="51" t="s">
+      <c r="K88" s="29" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="89" spans="5:11" s="39" customFormat="1" ht="57" x14ac:dyDescent="0.15">
-      <c r="E89" s="77">
+    <row r="89" spans="5:11" s="17" customFormat="1" ht="57" x14ac:dyDescent="0.15">
+      <c r="E89" s="55">
         <v>88</v>
       </c>
-      <c r="F89" s="77" t="s">
+      <c r="F89" s="55" t="s">
         <v>410</v>
       </c>
-      <c r="G89" s="77">
+      <c r="G89" s="55">
         <v>1</v>
       </c>
-      <c r="H89" s="90" t="s">
+      <c r="H89" s="68" t="s">
         <v>411</v>
       </c>
-      <c r="I89" s="78" t="s">
+      <c r="I89" s="56" t="s">
         <v>412</v>
       </c>
-      <c r="J89" s="78" t="s">
+      <c r="J89" s="56" t="s">
         <v>413</v>
       </c>
-      <c r="K89" s="78" t="s">
+      <c r="K89" s="56" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="90" spans="5:11" s="39" customFormat="1" ht="38" x14ac:dyDescent="0.15">
-      <c r="E90" s="77">
+    <row r="90" spans="5:11" s="17" customFormat="1" ht="38" x14ac:dyDescent="0.15">
+      <c r="E90" s="55">
         <v>89</v>
       </c>
-      <c r="F90" s="77" t="s">
+      <c r="F90" s="55" t="s">
         <v>415</v>
       </c>
-      <c r="G90" s="77">
+      <c r="G90" s="55">
         <v>3</v>
       </c>
-      <c r="H90" s="78" t="s">
+      <c r="H90" s="56" t="s">
         <v>416</v>
       </c>
-      <c r="I90" s="78" t="s">
+      <c r="I90" s="56" t="s">
         <v>417</v>
       </c>
-      <c r="J90" s="90" t="s">
+      <c r="J90" s="68" t="s">
         <v>418</v>
       </c>
-      <c r="K90" s="79" t="s">
+      <c r="K90" s="57" t="s">
         <v>419</v>
       </c>
     </row>
-    <row r="91" spans="5:11" s="30" customFormat="1" ht="114" x14ac:dyDescent="0.15">
-      <c r="E91" s="49">
+    <row r="91" spans="5:11" s="8" customFormat="1" ht="114" x14ac:dyDescent="0.15">
+      <c r="E91" s="27">
         <v>90</v>
       </c>
-      <c r="F91" s="49" t="s">
+      <c r="F91" s="27" t="s">
         <v>420</v>
       </c>
-      <c r="G91" s="49">
+      <c r="G91" s="27">
         <v>1</v>
       </c>
-      <c r="H91" s="80" t="s">
+      <c r="H91" s="58" t="s">
         <v>421</v>
       </c>
-      <c r="I91" s="51" t="s">
+      <c r="I91" s="29" t="s">
         <v>422</v>
       </c>
-      <c r="J91" s="51" t="s">
+      <c r="J91" s="29" t="s">
         <v>423</v>
       </c>
-      <c r="K91" s="51" t="s">
+      <c r="K91" s="29" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="92" spans="5:11" s="30" customFormat="1" ht="95" x14ac:dyDescent="0.15">
-      <c r="E92" s="49">
+    <row r="92" spans="5:11" s="8" customFormat="1" ht="95" x14ac:dyDescent="0.15">
+      <c r="E92" s="27">
         <v>91</v>
       </c>
-      <c r="F92" s="49" t="s">
+      <c r="F92" s="27" t="s">
         <v>425</v>
       </c>
-      <c r="G92" s="49">
+      <c r="G92" s="27">
         <v>1</v>
       </c>
-      <c r="H92" s="80" t="s">
+      <c r="H92" s="58" t="s">
         <v>426</v>
       </c>
-      <c r="I92" s="51" t="s">
+      <c r="I92" s="29" t="s">
         <v>427</v>
       </c>
-      <c r="J92" s="51" t="s">
+      <c r="J92" s="29" t="s">
         <v>428</v>
       </c>
-      <c r="K92" s="51" t="s">
+      <c r="K92" s="29" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="93" spans="5:11" s="30" customFormat="1" ht="95" x14ac:dyDescent="0.15">
-      <c r="E93" s="49">
+    <row r="93" spans="5:11" s="8" customFormat="1" ht="95" x14ac:dyDescent="0.15">
+      <c r="E93" s="27">
         <v>92</v>
       </c>
-      <c r="F93" s="49" t="s">
+      <c r="F93" s="27" t="s">
         <v>430</v>
       </c>
-      <c r="G93" s="49">
+      <c r="G93" s="27">
         <v>1</v>
       </c>
-      <c r="H93" s="80" t="s">
+      <c r="H93" s="58" t="s">
         <v>431</v>
       </c>
-      <c r="I93" s="51" t="s">
+      <c r="I93" s="29" t="s">
         <v>432</v>
       </c>
-      <c r="J93" s="51" t="s">
+      <c r="J93" s="29" t="s">
         <v>433</v>
       </c>
-      <c r="K93" s="51" t="s">
+      <c r="K93" s="29" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="94" spans="5:11" s="30" customFormat="1" ht="76" x14ac:dyDescent="0.15">
-      <c r="E94" s="49">
+    <row r="94" spans="5:11" s="8" customFormat="1" ht="76" x14ac:dyDescent="0.15">
+      <c r="E94" s="27">
         <v>93</v>
       </c>
-      <c r="F94" s="49" t="s">
+      <c r="F94" s="27" t="s">
         <v>435</v>
       </c>
-      <c r="G94" s="49">
+      <c r="G94" s="27">
         <v>1</v>
       </c>
-      <c r="H94" s="80" t="s">
+      <c r="H94" s="58" t="s">
         <v>436</v>
       </c>
-      <c r="I94" s="51" t="s">
+      <c r="I94" s="29" t="s">
         <v>437</v>
       </c>
-      <c r="J94" s="51" t="s">
+      <c r="J94" s="29" t="s">
         <v>438</v>
       </c>
-      <c r="K94" s="51" t="s">
+      <c r="K94" s="29" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="95" spans="5:11" s="30" customFormat="1" ht="82" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E95" s="49">
+    <row r="95" spans="5:11" s="8" customFormat="1" ht="82" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E95" s="27">
         <v>94</v>
       </c>
-      <c r="F95" s="49" t="s">
+      <c r="F95" s="27" t="s">
         <v>435</v>
       </c>
-      <c r="G95" s="49">
+      <c r="G95" s="27">
         <v>1</v>
       </c>
-      <c r="H95" s="80" t="s">
+      <c r="H95" s="58" t="s">
         <v>436</v>
       </c>
-      <c r="I95" s="51" t="s">
+      <c r="I95" s="29" t="s">
         <v>440</v>
       </c>
-      <c r="J95" s="51" t="s">
+      <c r="J95" s="29" t="s">
         <v>438</v>
       </c>
-      <c r="K95" s="51" t="s">
+      <c r="K95" s="29" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="96" spans="5:11" s="30" customFormat="1" ht="114" x14ac:dyDescent="0.15">
-      <c r="E96" s="49">
+    <row r="96" spans="5:11" s="8" customFormat="1" ht="114" x14ac:dyDescent="0.15">
+      <c r="E96" s="27">
         <v>95</v>
       </c>
-      <c r="F96" s="49" t="s">
+      <c r="F96" s="27" t="s">
         <v>441</v>
       </c>
-      <c r="G96" s="49">
+      <c r="G96" s="27">
         <v>3</v>
       </c>
-      <c r="H96" s="51" t="s">
+      <c r="H96" s="29" t="s">
         <v>442</v>
       </c>
-      <c r="I96" s="51" t="s">
+      <c r="I96" s="29" t="s">
         <v>443</v>
       </c>
-      <c r="J96" s="80" t="s">
+      <c r="J96" s="58" t="s">
         <v>444</v>
       </c>
-      <c r="K96" s="51" t="s">
+      <c r="K96" s="29" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="97" spans="1:11" s="30" customFormat="1" ht="95" x14ac:dyDescent="0.15">
-      <c r="E97" s="53">
+    <row r="97" spans="1:11" s="8" customFormat="1" ht="95" x14ac:dyDescent="0.15">
+      <c r="E97" s="31">
         <v>96</v>
       </c>
-      <c r="F97" s="53" t="s">
+      <c r="F97" s="31" t="s">
         <v>446</v>
       </c>
-      <c r="G97" s="53">
+      <c r="G97" s="31">
         <v>1</v>
       </c>
-      <c r="H97" s="81" t="s">
+      <c r="H97" s="59" t="s">
         <v>447</v>
       </c>
-      <c r="I97" s="54" t="s">
+      <c r="I97" s="32" t="s">
         <v>448</v>
       </c>
-      <c r="J97" s="54" t="s">
+      <c r="J97" s="32" t="s">
         <v>449</v>
       </c>
-      <c r="K97" s="54" t="s">
+      <c r="K97" s="32" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="98" spans="1:11" ht="38" x14ac:dyDescent="0.2">
-      <c r="A98" s="92"/>
-      <c r="B98" s="92"/>
-      <c r="C98" s="92"/>
-      <c r="D98" s="97"/>
-      <c r="E98" s="96">
+      <c r="A98" s="69"/>
+      <c r="B98" s="69"/>
+      <c r="C98" s="69"/>
+      <c r="D98" s="74"/>
+      <c r="E98" s="73">
         <v>97</v>
       </c>
-      <c r="F98" s="93" t="s">
+      <c r="F98" s="70" t="s">
         <v>179</v>
       </c>
-      <c r="G98" s="94">
+      <c r="G98" s="71">
         <v>4</v>
       </c>
-      <c r="H98" s="95" t="s">
+      <c r="H98" s="72" t="s">
         <v>180</v>
       </c>
-      <c r="I98" s="95" t="s">
+      <c r="I98" s="72" t="s">
         <v>181</v>
       </c>
-      <c r="J98" s="95" t="s">
+      <c r="J98" s="72" t="s">
         <v>182</v>
       </c>
-      <c r="K98" s="98" t="s">
+      <c r="K98" s="75" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:11" ht="38" x14ac:dyDescent="0.2">
-      <c r="A99" s="92"/>
-      <c r="B99" s="92"/>
-      <c r="C99" s="92"/>
-      <c r="D99" s="97"/>
-      <c r="E99" s="96">
+      <c r="A99" s="69"/>
+      <c r="B99" s="69"/>
+      <c r="C99" s="69"/>
+      <c r="D99" s="74"/>
+      <c r="E99" s="73">
         <v>98</v>
       </c>
-      <c r="F99" s="93" t="s">
+      <c r="F99" s="70" t="s">
         <v>184</v>
       </c>
-      <c r="G99" s="94">
+      <c r="G99" s="71">
         <v>4</v>
       </c>
-      <c r="H99" s="95" t="s">
+      <c r="H99" s="72" t="s">
         <v>185</v>
       </c>
-      <c r="I99" s="95" t="s">
+      <c r="I99" s="72" t="s">
         <v>186</v>
       </c>
-      <c r="J99" s="95" t="s">
+      <c r="J99" s="72" t="s">
         <v>187</v>
       </c>
-      <c r="K99" s="98" t="s">
+      <c r="K99" s="75" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="100" spans="1:11" ht="57" x14ac:dyDescent="0.2">
-      <c r="A100" s="92"/>
-      <c r="B100" s="92"/>
-      <c r="C100" s="92"/>
-      <c r="D100" s="97"/>
-      <c r="E100" s="96">
+      <c r="A100" s="69"/>
+      <c r="B100" s="69"/>
+      <c r="C100" s="69"/>
+      <c r="D100" s="74"/>
+      <c r="E100" s="73">
         <v>99</v>
       </c>
-      <c r="F100" s="93" t="s">
+      <c r="F100" s="70" t="s">
         <v>194</v>
       </c>
-      <c r="G100" s="94">
+      <c r="G100" s="71">
         <v>1</v>
       </c>
-      <c r="H100" s="98" t="s">
+      <c r="H100" s="75" t="s">
         <v>195</v>
       </c>
-      <c r="I100" s="95" t="s">
+      <c r="I100" s="72" t="s">
         <v>196</v>
       </c>
-      <c r="J100" s="95" t="s">
+      <c r="J100" s="72" t="s">
         <v>197</v>
       </c>
-      <c r="K100" s="95" t="s">
+      <c r="K100" s="72" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="101" spans="1:11" ht="38" x14ac:dyDescent="0.2">
-      <c r="A101" s="92"/>
-      <c r="B101" s="92"/>
-      <c r="C101" s="92"/>
-      <c r="D101" s="97"/>
-      <c r="E101" s="96">
+      <c r="A101" s="69"/>
+      <c r="B101" s="69"/>
+      <c r="C101" s="69"/>
+      <c r="D101" s="74"/>
+      <c r="E101" s="73">
         <v>100</v>
       </c>
-      <c r="F101" s="93" t="s">
+      <c r="F101" s="70" t="s">
         <v>199</v>
       </c>
-      <c r="G101" s="94">
+      <c r="G101" s="71">
         <v>1</v>
       </c>
-      <c r="H101" s="98" t="s">
+      <c r="H101" s="75" t="s">
         <v>200</v>
       </c>
-      <c r="I101" s="95" t="s">
+      <c r="I101" s="72" t="s">
         <v>201</v>
       </c>
-      <c r="J101" s="95" t="s">
+      <c r="J101" s="72" t="s">
         <v>202</v>
       </c>
-      <c r="K101" s="95" t="s">
+      <c r="K101" s="72" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="102" spans="1:11" ht="38" x14ac:dyDescent="0.2">
-      <c r="A102" s="92"/>
-      <c r="B102" s="92"/>
-      <c r="C102" s="92"/>
-      <c r="D102" s="97"/>
-      <c r="E102" s="96">
+      <c r="A102" s="69"/>
+      <c r="B102" s="69"/>
+      <c r="C102" s="69"/>
+      <c r="D102" s="74"/>
+      <c r="E102" s="73">
         <v>101</v>
       </c>
-      <c r="F102" s="93" t="s">
+      <c r="F102" s="70" t="s">
         <v>205</v>
       </c>
-      <c r="G102" s="94">
+      <c r="G102" s="71">
         <v>2</v>
       </c>
-      <c r="H102" s="95" t="s">
+      <c r="H102" s="72" t="s">
         <v>206</v>
       </c>
-      <c r="I102" s="98" t="s">
+      <c r="I102" s="75" t="s">
         <v>207</v>
       </c>
-      <c r="J102" s="95" t="s">
+      <c r="J102" s="72" t="s">
         <v>208</v>
       </c>
-      <c r="K102" s="95" t="s">
+      <c r="K102" s="72" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="103" spans="1:11" ht="38" x14ac:dyDescent="0.2">
-      <c r="A103" s="92"/>
-      <c r="B103" s="92"/>
-      <c r="C103" s="92"/>
-      <c r="D103" s="97"/>
-      <c r="E103" s="96">
+      <c r="A103" s="69"/>
+      <c r="B103" s="69"/>
+      <c r="C103" s="69"/>
+      <c r="D103" s="74"/>
+      <c r="E103" s="73">
         <v>102</v>
       </c>
-      <c r="F103" s="93" t="s">
+      <c r="F103" s="70" t="s">
+        <v>451</v>
+      </c>
+      <c r="G103" s="71">
+        <v>3</v>
+      </c>
+      <c r="H103" s="72" t="s">
+        <v>452</v>
+      </c>
+      <c r="I103" s="72" t="s">
+        <v>453</v>
+      </c>
+      <c r="J103" s="75" t="s">
+        <v>200</v>
+      </c>
+      <c r="K103" s="72" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" ht="19" x14ac:dyDescent="0.2">
+      <c r="A104" s="69"/>
+      <c r="B104" s="69"/>
+      <c r="C104" s="69"/>
+      <c r="D104" s="74"/>
+      <c r="E104" s="73">
+        <v>103</v>
+      </c>
+      <c r="F104" s="70" t="s">
+        <v>455</v>
+      </c>
+      <c r="G104" s="71">
+        <v>2</v>
+      </c>
+      <c r="H104" s="72" t="s">
+        <v>456</v>
+      </c>
+      <c r="I104" s="75" t="s">
+        <v>457</v>
+      </c>
+      <c r="J104" s="72" t="s">
+        <v>458</v>
+      </c>
+      <c r="K104" s="72" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" ht="76" x14ac:dyDescent="0.2">
+      <c r="A105" s="69"/>
+      <c r="B105" s="69"/>
+      <c r="C105" s="69"/>
+      <c r="D105" s="74"/>
+      <c r="E105" s="73">
+        <v>104</v>
+      </c>
+      <c r="F105" s="70" t="s">
+        <v>460</v>
+      </c>
+      <c r="G105" s="71">
+        <v>3</v>
+      </c>
+      <c r="H105" s="72" t="s">
+        <v>461</v>
+      </c>
+      <c r="I105" s="72" t="s">
+        <v>462</v>
+      </c>
+      <c r="J105" s="75" t="s">
         <v>463</v>
       </c>
-      <c r="G103" s="94">
+      <c r="K105" s="72" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" ht="57" x14ac:dyDescent="0.2">
+      <c r="A106" s="69"/>
+      <c r="B106" s="69"/>
+      <c r="C106" s="69"/>
+      <c r="D106" s="74"/>
+      <c r="E106" s="73">
+        <v>105</v>
+      </c>
+      <c r="F106" s="70" t="s">
+        <v>465</v>
+      </c>
+      <c r="G106" s="71">
         <v>3</v>
       </c>
-      <c r="H103" s="95" t="s">
-        <v>464</v>
-      </c>
-      <c r="I103" s="95" t="s">
-        <v>465</v>
-      </c>
-      <c r="J103" s="98" t="s">
-        <v>200</v>
-      </c>
-      <c r="K103" s="95" t="s">
+      <c r="H106" s="72" t="s">
         <v>466</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" ht="19" x14ac:dyDescent="0.2">
-      <c r="A104" s="92"/>
-      <c r="B104" s="92"/>
-      <c r="C104" s="92"/>
-      <c r="D104" s="97"/>
-      <c r="E104" s="96">
-        <v>103</v>
-      </c>
-      <c r="F104" s="93" t="s">
+      <c r="I106" s="72" t="s">
         <v>467</v>
       </c>
-      <c r="G104" s="94">
+      <c r="J106" s="75" t="s">
+        <v>468</v>
+      </c>
+      <c r="K106" s="72" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" ht="38" x14ac:dyDescent="0.2">
+      <c r="A107" s="69"/>
+      <c r="B107" s="69"/>
+      <c r="C107" s="69"/>
+      <c r="D107" s="74"/>
+      <c r="E107" s="73">
+        <v>106</v>
+      </c>
+      <c r="F107" s="70" t="s">
+        <v>470</v>
+      </c>
+      <c r="G107" s="71">
+        <v>4</v>
+      </c>
+      <c r="H107" s="72" t="s">
+        <v>471</v>
+      </c>
+      <c r="I107" s="72" t="s">
+        <v>472</v>
+      </c>
+      <c r="J107" s="72" t="s">
+        <v>473</v>
+      </c>
+      <c r="K107" s="75" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" ht="76" x14ac:dyDescent="0.2">
+      <c r="A108" s="69"/>
+      <c r="B108" s="69"/>
+      <c r="C108" s="69"/>
+      <c r="D108" s="74"/>
+      <c r="E108" s="73">
+        <v>107</v>
+      </c>
+      <c r="F108" s="70" t="s">
+        <v>230</v>
+      </c>
+      <c r="G108" s="71">
+        <v>4</v>
+      </c>
+      <c r="H108" s="72" t="s">
+        <v>231</v>
+      </c>
+      <c r="I108" s="72" t="s">
+        <v>232</v>
+      </c>
+      <c r="J108" s="72" t="s">
+        <v>233</v>
+      </c>
+      <c r="K108" s="75" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" ht="38" x14ac:dyDescent="0.2">
+      <c r="A109" s="69"/>
+      <c r="B109" s="69"/>
+      <c r="C109" s="69"/>
+      <c r="D109" s="74"/>
+      <c r="E109" s="73">
+        <v>108</v>
+      </c>
+      <c r="F109" s="70" t="s">
+        <v>235</v>
+      </c>
+      <c r="G109" s="71">
+        <v>3</v>
+      </c>
+      <c r="H109" s="72" t="s">
+        <v>236</v>
+      </c>
+      <c r="I109" s="72" t="s">
+        <v>237</v>
+      </c>
+      <c r="J109" s="75" t="s">
+        <v>238</v>
+      </c>
+      <c r="K109" s="72" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" ht="133" x14ac:dyDescent="0.2">
+      <c r="A110" s="69"/>
+      <c r="B110" s="69"/>
+      <c r="C110" s="69"/>
+      <c r="D110" s="74"/>
+      <c r="E110" s="73">
+        <v>109</v>
+      </c>
+      <c r="F110" s="70" t="s">
+        <v>475</v>
+      </c>
+      <c r="G110" s="71">
+        <v>4</v>
+      </c>
+      <c r="H110" s="72" t="s">
+        <v>476</v>
+      </c>
+      <c r="I110" s="72" t="s">
+        <v>477</v>
+      </c>
+      <c r="J110" s="72" t="s">
+        <v>478</v>
+      </c>
+      <c r="K110" s="75" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="95" x14ac:dyDescent="0.2">
+      <c r="A111" s="69"/>
+      <c r="B111" s="69"/>
+      <c r="C111" s="69"/>
+      <c r="D111" s="74"/>
+      <c r="E111" s="73">
+        <v>110</v>
+      </c>
+      <c r="F111" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="G111" s="71">
+        <v>4</v>
+      </c>
+      <c r="H111" s="72" t="s">
+        <v>241</v>
+      </c>
+      <c r="I111" s="72" t="s">
+        <v>242</v>
+      </c>
+      <c r="J111" s="72" t="s">
+        <v>243</v>
+      </c>
+      <c r="K111" s="75" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" ht="76" x14ac:dyDescent="0.2">
+      <c r="A112" s="69"/>
+      <c r="B112" s="69"/>
+      <c r="C112" s="69"/>
+      <c r="D112" s="74"/>
+      <c r="E112" s="73">
+        <v>111</v>
+      </c>
+      <c r="F112" s="70" t="s">
+        <v>245</v>
+      </c>
+      <c r="G112" s="71">
+        <v>4</v>
+      </c>
+      <c r="H112" s="72" t="s">
+        <v>246</v>
+      </c>
+      <c r="I112" s="72" t="s">
+        <v>247</v>
+      </c>
+      <c r="J112" s="72" t="s">
+        <v>248</v>
+      </c>
+      <c r="K112" s="75" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" ht="38" x14ac:dyDescent="0.2">
+      <c r="A113" s="69"/>
+      <c r="B113" s="69"/>
+      <c r="C113" s="69"/>
+      <c r="D113" s="74"/>
+      <c r="E113" s="73">
+        <v>112</v>
+      </c>
+      <c r="F113" s="70" t="s">
+        <v>480</v>
+      </c>
+      <c r="G113" s="71">
+        <v>4</v>
+      </c>
+      <c r="H113" s="72" t="s">
+        <v>481</v>
+      </c>
+      <c r="I113" s="72" t="s">
+        <v>482</v>
+      </c>
+      <c r="J113" s="72" t="s">
+        <v>483</v>
+      </c>
+      <c r="K113" s="75" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" ht="57" x14ac:dyDescent="0.2">
+      <c r="A114" s="69"/>
+      <c r="B114" s="69"/>
+      <c r="C114" s="69"/>
+      <c r="D114" s="74"/>
+      <c r="E114" s="73">
+        <v>113</v>
+      </c>
+      <c r="F114" s="70" t="s">
+        <v>485</v>
+      </c>
+      <c r="G114" s="71">
+        <v>1</v>
+      </c>
+      <c r="H114" s="75" t="s">
+        <v>486</v>
+      </c>
+      <c r="I114" s="72" t="s">
+        <v>487</v>
+      </c>
+      <c r="J114" s="72" t="s">
+        <v>488</v>
+      </c>
+      <c r="K114" s="72" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" ht="38" x14ac:dyDescent="0.2">
+      <c r="A115" s="69"/>
+      <c r="B115" s="69"/>
+      <c r="C115" s="69"/>
+      <c r="D115" s="74"/>
+      <c r="E115" s="73">
+        <v>114</v>
+      </c>
+      <c r="F115" s="70" t="s">
+        <v>490</v>
+      </c>
+      <c r="G115" s="71">
+        <v>3</v>
+      </c>
+      <c r="H115" s="72" t="s">
+        <v>491</v>
+      </c>
+      <c r="I115" s="72" t="s">
+        <v>492</v>
+      </c>
+      <c r="J115" s="75" t="s">
+        <v>493</v>
+      </c>
+      <c r="K115" s="72" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" ht="57" x14ac:dyDescent="0.2">
+      <c r="A116" s="69"/>
+      <c r="B116" s="69"/>
+      <c r="C116" s="69"/>
+      <c r="D116" s="74"/>
+      <c r="E116" s="73">
+        <v>115</v>
+      </c>
+      <c r="F116" s="70" t="s">
+        <v>265</v>
+      </c>
+      <c r="G116" s="71">
         <v>2</v>
       </c>
-      <c r="H104" s="95" t="s">
-        <v>468</v>
-      </c>
-      <c r="I104" s="98" t="s">
-        <v>469</v>
-      </c>
-      <c r="J104" s="95" t="s">
-        <v>470</v>
-      </c>
-      <c r="K104" s="95" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" ht="76" x14ac:dyDescent="0.2">
-      <c r="A105" s="92"/>
-      <c r="B105" s="92"/>
-      <c r="C105" s="92"/>
-      <c r="D105" s="97"/>
-      <c r="E105" s="96">
-        <v>104</v>
-      </c>
-      <c r="F105" s="93" t="s">
-        <v>472</v>
-      </c>
-      <c r="G105" s="94">
-        <v>3</v>
-      </c>
-      <c r="H105" s="95" t="s">
-        <v>473</v>
-      </c>
-      <c r="I105" s="95" t="s">
-        <v>474</v>
-      </c>
-      <c r="J105" s="98" t="s">
-        <v>475</v>
-      </c>
-      <c r="K105" s="95" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" ht="57" x14ac:dyDescent="0.2">
-      <c r="A106" s="92"/>
-      <c r="B106" s="92"/>
-      <c r="C106" s="92"/>
-      <c r="D106" s="97"/>
-      <c r="E106" s="96">
-        <v>105</v>
-      </c>
-      <c r="F106" s="93" t="s">
-        <v>477</v>
-      </c>
-      <c r="G106" s="94">
-        <v>3</v>
-      </c>
-      <c r="H106" s="95" t="s">
-        <v>478</v>
-      </c>
-      <c r="I106" s="95" t="s">
-        <v>479</v>
-      </c>
-      <c r="J106" s="98" t="s">
-        <v>480</v>
-      </c>
-      <c r="K106" s="95" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" ht="38" x14ac:dyDescent="0.2">
-      <c r="A107" s="92"/>
-      <c r="B107" s="92"/>
-      <c r="C107" s="92"/>
-      <c r="D107" s="97"/>
-      <c r="E107" s="96">
-        <v>106</v>
-      </c>
-      <c r="F107" s="93" t="s">
-        <v>483</v>
-      </c>
-      <c r="G107" s="94">
+      <c r="H116" s="72" t="s">
+        <v>266</v>
+      </c>
+      <c r="I116" s="75" t="s">
+        <v>267</v>
+      </c>
+      <c r="J116" s="72" t="s">
+        <v>268</v>
+      </c>
+      <c r="K116" s="72" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="95" x14ac:dyDescent="0.2">
+      <c r="A117" s="69"/>
+      <c r="B117" s="69"/>
+      <c r="C117" s="69"/>
+      <c r="D117" s="74"/>
+      <c r="E117" s="73">
+        <v>116</v>
+      </c>
+      <c r="F117" s="70" t="s">
+        <v>495</v>
+      </c>
+      <c r="G117" s="71">
         <v>4</v>
       </c>
-      <c r="H107" s="95" t="s">
-        <v>484</v>
-      </c>
-      <c r="I107" s="95" t="s">
-        <v>485</v>
-      </c>
-      <c r="J107" s="95" t="s">
-        <v>486</v>
-      </c>
-      <c r="K107" s="98" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" ht="76" x14ac:dyDescent="0.2">
-      <c r="A108" s="92"/>
-      <c r="B108" s="92"/>
-      <c r="C108" s="92"/>
-      <c r="D108" s="97"/>
-      <c r="E108" s="96">
-        <v>107</v>
-      </c>
-      <c r="F108" s="93" t="s">
-        <v>230</v>
-      </c>
-      <c r="G108" s="94">
+      <c r="H117" s="72" t="s">
+        <v>496</v>
+      </c>
+      <c r="I117" s="72" t="s">
+        <v>497</v>
+      </c>
+      <c r="J117" s="72" t="s">
+        <v>498</v>
+      </c>
+      <c r="K117" s="75" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" ht="95" x14ac:dyDescent="0.2">
+      <c r="A118" s="69"/>
+      <c r="B118" s="69"/>
+      <c r="C118" s="69"/>
+      <c r="D118" s="74"/>
+      <c r="E118" s="73">
+        <v>117</v>
+      </c>
+      <c r="F118" s="70" t="s">
+        <v>500</v>
+      </c>
+      <c r="G118" s="71">
+        <v>2</v>
+      </c>
+      <c r="H118" s="72" t="s">
+        <v>203</v>
+      </c>
+      <c r="I118" s="75" t="s">
+        <v>202</v>
+      </c>
+      <c r="J118" s="72" t="s">
+        <v>501</v>
+      </c>
+      <c r="K118" s="72" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" ht="57" x14ac:dyDescent="0.2">
+      <c r="A119" s="69"/>
+      <c r="B119" s="69"/>
+      <c r="C119" s="69"/>
+      <c r="D119" s="74"/>
+      <c r="E119" s="73">
+        <v>118</v>
+      </c>
+      <c r="F119" s="70" t="s">
+        <v>503</v>
+      </c>
+      <c r="G119" s="71">
+        <v>2</v>
+      </c>
+      <c r="H119" s="72" t="s">
+        <v>504</v>
+      </c>
+      <c r="I119" s="75" t="s">
+        <v>505</v>
+      </c>
+      <c r="J119" s="72" t="s">
+        <v>506</v>
+      </c>
+      <c r="K119" s="72" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" ht="38" x14ac:dyDescent="0.2">
+      <c r="A120" s="69"/>
+      <c r="B120" s="69"/>
+      <c r="C120" s="69"/>
+      <c r="D120" s="74"/>
+      <c r="E120" s="73">
+        <v>119</v>
+      </c>
+      <c r="F120" s="70" t="s">
+        <v>508</v>
+      </c>
+      <c r="G120" s="71">
         <v>4</v>
       </c>
-      <c r="H108" s="95" t="s">
-        <v>231</v>
-      </c>
-      <c r="I108" s="95" t="s">
-        <v>232</v>
-      </c>
-      <c r="J108" s="95" t="s">
-        <v>233</v>
-      </c>
-      <c r="K108" s="98" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" ht="38" x14ac:dyDescent="0.2">
-      <c r="A109" s="92"/>
-      <c r="B109" s="92"/>
-      <c r="C109" s="92"/>
-      <c r="D109" s="97"/>
-      <c r="E109" s="96">
-        <v>108</v>
-      </c>
-      <c r="F109" s="93" t="s">
-        <v>235</v>
-      </c>
-      <c r="G109" s="94">
-        <v>3</v>
-      </c>
-      <c r="H109" s="95" t="s">
-        <v>236</v>
-      </c>
-      <c r="I109" s="95" t="s">
-        <v>237</v>
-      </c>
-      <c r="J109" s="98" t="s">
-        <v>238</v>
-      </c>
-      <c r="K109" s="95" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" ht="133" x14ac:dyDescent="0.2">
-      <c r="A110" s="92"/>
-      <c r="B110" s="92"/>
-      <c r="C110" s="92"/>
-      <c r="D110" s="97"/>
-      <c r="E110" s="96">
-        <v>109</v>
-      </c>
-      <c r="F110" s="93" t="s">
-        <v>488</v>
-      </c>
-      <c r="G110" s="94">
-        <v>4</v>
-      </c>
-      <c r="H110" s="95" t="s">
-        <v>489</v>
-      </c>
-      <c r="I110" s="95" t="s">
-        <v>490</v>
-      </c>
-      <c r="J110" s="95" t="s">
-        <v>491</v>
-      </c>
-      <c r="K110" s="98" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="95" x14ac:dyDescent="0.2">
-      <c r="A111" s="92"/>
-      <c r="B111" s="92"/>
-      <c r="C111" s="92"/>
-      <c r="D111" s="97"/>
-      <c r="E111" s="96">
-        <v>110</v>
-      </c>
-      <c r="F111" s="93" t="s">
-        <v>240</v>
-      </c>
-      <c r="G111" s="94">
-        <v>4</v>
-      </c>
-      <c r="H111" s="95" t="s">
-        <v>241</v>
-      </c>
-      <c r="I111" s="95" t="s">
-        <v>242</v>
-      </c>
-      <c r="J111" s="95" t="s">
-        <v>243</v>
-      </c>
-      <c r="K111" s="98" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" ht="76" x14ac:dyDescent="0.2">
-      <c r="A112" s="92"/>
-      <c r="B112" s="92"/>
-      <c r="C112" s="92"/>
-      <c r="D112" s="97"/>
-      <c r="E112" s="96">
-        <v>111</v>
-      </c>
-      <c r="F112" s="93" t="s">
-        <v>245</v>
-      </c>
-      <c r="G112" s="94">
-        <v>4</v>
-      </c>
-      <c r="H112" s="95" t="s">
-        <v>246</v>
-      </c>
-      <c r="I112" s="95" t="s">
-        <v>247</v>
-      </c>
-      <c r="J112" s="95" t="s">
-        <v>248</v>
-      </c>
-      <c r="K112" s="98" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" ht="38" x14ac:dyDescent="0.2">
-      <c r="A113" s="92"/>
-      <c r="B113" s="92"/>
-      <c r="C113" s="92"/>
-      <c r="D113" s="97"/>
-      <c r="E113" s="96">
-        <v>112</v>
-      </c>
-      <c r="F113" s="93" t="s">
-        <v>493</v>
-      </c>
-      <c r="G113" s="94">
-        <v>4</v>
-      </c>
-      <c r="H113" s="95" t="s">
-        <v>494</v>
-      </c>
-      <c r="I113" s="95" t="s">
-        <v>495</v>
-      </c>
-      <c r="J113" s="95" t="s">
-        <v>496</v>
-      </c>
-      <c r="K113" s="98" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" ht="57" x14ac:dyDescent="0.2">
-      <c r="A114" s="92"/>
-      <c r="B114" s="92"/>
-      <c r="C114" s="92"/>
-      <c r="D114" s="97"/>
-      <c r="E114" s="96">
-        <v>113</v>
-      </c>
-      <c r="F114" s="93" t="s">
-        <v>498</v>
-      </c>
-      <c r="G114" s="94">
+      <c r="H120" s="72" t="s">
+        <v>509</v>
+      </c>
+      <c r="I120" s="72" t="s">
+        <v>510</v>
+      </c>
+      <c r="J120" s="72" t="s">
+        <v>511</v>
+      </c>
+      <c r="K120" s="75" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" ht="38" x14ac:dyDescent="0.2">
+      <c r="A121" s="69"/>
+      <c r="B121" s="69"/>
+      <c r="C121" s="69"/>
+      <c r="D121" s="74"/>
+      <c r="E121" s="73">
+        <v>120</v>
+      </c>
+      <c r="F121" s="70" t="s">
+        <v>513</v>
+      </c>
+      <c r="G121" s="71">
         <v>1</v>
       </c>
-      <c r="H114" s="98" t="s">
-        <v>499</v>
-      </c>
-      <c r="I114" s="95" t="s">
-        <v>500</v>
-      </c>
-      <c r="J114" s="95" t="s">
-        <v>501</v>
-      </c>
-      <c r="K114" s="95" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11" ht="38" x14ac:dyDescent="0.2">
-      <c r="A115" s="92"/>
-      <c r="B115" s="92"/>
-      <c r="C115" s="92"/>
-      <c r="D115" s="97"/>
-      <c r="E115" s="96">
-        <v>114</v>
-      </c>
-      <c r="F115" s="93" t="s">
-        <v>503</v>
-      </c>
-      <c r="G115" s="94">
-        <v>3</v>
-      </c>
-      <c r="H115" s="95" t="s">
-        <v>504</v>
-      </c>
-      <c r="I115" s="95" t="s">
-        <v>505</v>
-      </c>
-      <c r="J115" s="98" t="s">
-        <v>506</v>
-      </c>
-      <c r="K115" s="95" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11" ht="57" x14ac:dyDescent="0.2">
-      <c r="A116" s="92"/>
-      <c r="B116" s="92"/>
-      <c r="C116" s="92"/>
-      <c r="D116" s="97"/>
-      <c r="E116" s="96">
-        <v>115</v>
-      </c>
-      <c r="F116" s="93" t="s">
-        <v>265</v>
-      </c>
-      <c r="G116" s="94">
-        <v>2</v>
-      </c>
-      <c r="H116" s="95" t="s">
-        <v>266</v>
-      </c>
-      <c r="I116" s="98" t="s">
-        <v>267</v>
-      </c>
-      <c r="J116" s="95" t="s">
-        <v>268</v>
-      </c>
-      <c r="K116" s="95" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11" ht="95" x14ac:dyDescent="0.2">
-      <c r="A117" s="92"/>
-      <c r="B117" s="92"/>
-      <c r="C117" s="92"/>
-      <c r="D117" s="97"/>
-      <c r="E117" s="96">
-        <v>116</v>
-      </c>
-      <c r="F117" s="93" t="s">
-        <v>508</v>
-      </c>
-      <c r="G117" s="94">
-        <v>4</v>
-      </c>
-      <c r="H117" s="95" t="s">
-        <v>509</v>
-      </c>
-      <c r="I117" s="95" t="s">
-        <v>510</v>
-      </c>
-      <c r="J117" s="95" t="s">
-        <v>511</v>
-      </c>
-      <c r="K117" s="98" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11" ht="95" x14ac:dyDescent="0.2">
-      <c r="A118" s="92"/>
-      <c r="B118" s="92"/>
-      <c r="C118" s="92"/>
-      <c r="D118" s="97"/>
-      <c r="E118" s="96">
-        <v>117</v>
-      </c>
-      <c r="F118" s="93" t="s">
-        <v>513</v>
-      </c>
-      <c r="G118" s="94">
-        <v>2</v>
-      </c>
-      <c r="H118" s="95" t="s">
-        <v>203</v>
-      </c>
-      <c r="I118" s="98" t="s">
-        <v>202</v>
-      </c>
-      <c r="J118" s="95" t="s">
+      <c r="H121" s="75" t="s">
         <v>514</v>
       </c>
-      <c r="K118" s="95" t="s">
+      <c r="I121" s="72" t="s">
         <v>515</v>
       </c>
-    </row>
-    <row r="119" spans="1:11" ht="57" x14ac:dyDescent="0.2">
-      <c r="A119" s="92"/>
-      <c r="B119" s="92"/>
-      <c r="C119" s="92"/>
-      <c r="D119" s="97"/>
-      <c r="E119" s="96">
-        <v>118</v>
-      </c>
-      <c r="F119" s="93" t="s">
+      <c r="J121" s="72" t="s">
         <v>516</v>
       </c>
-      <c r="G119" s="94">
-        <v>2</v>
-      </c>
-      <c r="H119" s="95" t="s">
+      <c r="K121" s="72" t="s">
         <v>517</v>
-      </c>
-      <c r="I119" s="98" t="s">
-        <v>518</v>
-      </c>
-      <c r="J119" s="95" t="s">
-        <v>519</v>
-      </c>
-      <c r="K119" s="95" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" ht="38" x14ac:dyDescent="0.2">
-      <c r="A120" s="92"/>
-      <c r="B120" s="92"/>
-      <c r="C120" s="92"/>
-      <c r="D120" s="97"/>
-      <c r="E120" s="96">
-        <v>119</v>
-      </c>
-      <c r="F120" s="93" t="s">
-        <v>521</v>
-      </c>
-      <c r="G120" s="94">
-        <v>4</v>
-      </c>
-      <c r="H120" s="95" t="s">
-        <v>522</v>
-      </c>
-      <c r="I120" s="95" t="s">
-        <v>523</v>
-      </c>
-      <c r="J120" s="95" t="s">
-        <v>524</v>
-      </c>
-      <c r="K120" s="98" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11" ht="38" x14ac:dyDescent="0.2">
-      <c r="A121" s="92"/>
-      <c r="B121" s="92"/>
-      <c r="C121" s="92"/>
-      <c r="D121" s="97"/>
-      <c r="E121" s="96">
-        <v>120</v>
-      </c>
-      <c r="F121" s="93" t="s">
-        <v>526</v>
-      </c>
-      <c r="G121" s="94">
-        <v>1</v>
-      </c>
-      <c r="H121" s="98" t="s">
-        <v>527</v>
-      </c>
-      <c r="I121" s="95" t="s">
-        <v>528</v>
-      </c>
-      <c r="J121" s="95" t="s">
-        <v>529</v>
-      </c>
-      <c r="K121" s="95" t="s">
-        <v>530</v>
       </c>
     </row>
   </sheetData>
@@ -5843,1005 +5562,6 @@
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="61" orientation="landscape" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:O30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="1" max="1" width="15" style="23" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="21.5" style="23" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5" style="23" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="31.83203125" style="23" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1640625" style="26" customWidth="1"/>
-    <col min="7" max="7" width="54.1640625" style="27" customWidth="1"/>
-    <col min="8" max="8" width="11.5" style="28" customWidth="1"/>
-    <col min="9" max="12" width="36.5" style="27" customWidth="1"/>
-    <col min="13" max="13" width="12.5" style="23" customWidth="1"/>
-    <col min="14" max="14" width="14.83203125" style="23" customWidth="1"/>
-    <col min="15" max="15" width="29.83203125" style="27" customWidth="1"/>
-    <col min="16" max="16384" width="9.1640625" style="23"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:15" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="F2" s="91" t="s">
-        <v>452</v>
-      </c>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="4"/>
-    </row>
-    <row r="3" spans="1:15" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="2"/>
-      <c r="E3" s="5" t="s">
-        <v>453</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="8"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-    </row>
-    <row r="4" spans="1:15" s="1" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B4" s="2"/>
-      <c r="E4" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>456</v>
-      </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="12"/>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-    </row>
-    <row r="5" spans="1:15" s="1" customFormat="1" ht="19.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="2"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-    </row>
-    <row r="6" spans="1:15" s="19" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>457</v>
-      </c>
-      <c r="F6" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="J6" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="K6" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="M6" s="17" t="s">
-        <v>458</v>
-      </c>
-      <c r="N6" s="18" t="s">
-        <v>459</v>
-      </c>
-      <c r="O6" s="16" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="A7" s="20"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="20"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F7" s="22">
-        <v>1</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="H7" s="22">
-        <v>4</v>
-      </c>
-      <c r="I7" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="J7" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="K7" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>183</v>
-      </c>
-      <c r="M7" s="22">
-        <v>1</v>
-      </c>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="A8" s="20"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F8" s="22">
-        <f t="shared" ref="F8:F22" si="0">F7+1</f>
-        <v>2</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="H8" s="22">
-        <v>4</v>
-      </c>
-      <c r="I8" s="22" t="s">
-        <v>185</v>
-      </c>
-      <c r="J8" s="22" t="s">
-        <v>186</v>
-      </c>
-      <c r="K8" s="22" t="s">
-        <v>187</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="M8" s="22">
-        <v>1</v>
-      </c>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="A9" s="20"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F9" s="22">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>194</v>
-      </c>
-      <c r="H9" s="22">
-        <v>1</v>
-      </c>
-      <c r="I9" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="J9" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="K9" s="22" t="s">
-        <v>197</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>198</v>
-      </c>
-      <c r="M9" s="22">
-        <v>1</v>
-      </c>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="A10" s="20"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F10" s="22">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="H10" s="22">
-        <v>1</v>
-      </c>
-      <c r="I10" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="J10" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="K10" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="M10" s="22">
-        <v>1</v>
-      </c>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="E11" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F11" s="22">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>205</v>
-      </c>
-      <c r="H11" s="22">
-        <v>2</v>
-      </c>
-      <c r="I11" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="J11" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="K11" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="M11" s="22">
-        <v>1</v>
-      </c>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="E12" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F12" s="22">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>463</v>
-      </c>
-      <c r="H12" s="22">
-        <v>3</v>
-      </c>
-      <c r="I12" s="22" t="s">
-        <v>464</v>
-      </c>
-      <c r="J12" s="22" t="s">
-        <v>465</v>
-      </c>
-      <c r="K12" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>466</v>
-      </c>
-      <c r="M12" s="22">
-        <v>1</v>
-      </c>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="E13" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F13" s="22">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>467</v>
-      </c>
-      <c r="H13" s="22">
-        <v>2</v>
-      </c>
-      <c r="I13" s="22" t="s">
-        <v>468</v>
-      </c>
-      <c r="J13" s="22" t="s">
-        <v>469</v>
-      </c>
-      <c r="K13" s="22" t="s">
-        <v>470</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>471</v>
-      </c>
-      <c r="M13" s="22">
-        <v>1</v>
-      </c>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="E14" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F14" s="22">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>472</v>
-      </c>
-      <c r="H14" s="22">
-        <v>3</v>
-      </c>
-      <c r="I14" s="22" t="s">
-        <v>473</v>
-      </c>
-      <c r="J14" s="22" t="s">
-        <v>474</v>
-      </c>
-      <c r="K14" s="22" t="s">
-        <v>475</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>476</v>
-      </c>
-      <c r="M14" s="22">
-        <v>1</v>
-      </c>
-      <c r="N14" s="22"/>
-      <c r="O14" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15" ht="54" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E15" s="29" t="s">
-        <v>461</v>
-      </c>
-      <c r="F15" s="29">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="G15" s="29" t="s">
-        <v>477</v>
-      </c>
-      <c r="H15" s="29">
-        <v>3</v>
-      </c>
-      <c r="I15" s="29" t="s">
-        <v>478</v>
-      </c>
-      <c r="J15" s="29" t="s">
-        <v>479</v>
-      </c>
-      <c r="K15" s="29" t="s">
-        <v>480</v>
-      </c>
-      <c r="L15" s="29" t="s">
-        <v>481</v>
-      </c>
-      <c r="M15" s="29">
-        <v>1</v>
-      </c>
-      <c r="N15" s="29" t="s">
-        <v>482</v>
-      </c>
-      <c r="O15" s="29" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="87.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E16" s="29" t="s">
-        <v>461</v>
-      </c>
-      <c r="F16" s="29">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="G16" s="29" t="s">
-        <v>483</v>
-      </c>
-      <c r="H16" s="29">
-        <v>4</v>
-      </c>
-      <c r="I16" s="29" t="s">
-        <v>484</v>
-      </c>
-      <c r="J16" s="29" t="s">
-        <v>485</v>
-      </c>
-      <c r="K16" s="29" t="s">
-        <v>486</v>
-      </c>
-      <c r="L16" s="29" t="s">
-        <v>487</v>
-      </c>
-      <c r="M16" s="29">
-        <v>1</v>
-      </c>
-      <c r="N16" s="29" t="s">
-        <v>482</v>
-      </c>
-      <c r="O16" s="29" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="17" spans="5:15" ht="60" x14ac:dyDescent="0.15">
-      <c r="E17" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F17" s="22">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="H17" s="22">
-        <v>4</v>
-      </c>
-      <c r="I17" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="J17" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="K17" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>234</v>
-      </c>
-      <c r="M17" s="22">
-        <v>2</v>
-      </c>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="18" spans="5:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="E18" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F18" s="22">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="G18" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="H18" s="22">
-        <v>3</v>
-      </c>
-      <c r="I18" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="J18" s="22" t="s">
-        <v>237</v>
-      </c>
-      <c r="K18" s="22" t="s">
-        <v>238</v>
-      </c>
-      <c r="L18" s="22" t="s">
-        <v>239</v>
-      </c>
-      <c r="M18" s="22">
-        <v>2</v>
-      </c>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="19" spans="5:15" ht="90" x14ac:dyDescent="0.15">
-      <c r="E19" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F19" s="22">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="G19" s="22" t="s">
-        <v>488</v>
-      </c>
-      <c r="H19" s="22">
-        <v>4</v>
-      </c>
-      <c r="I19" s="22" t="s">
-        <v>489</v>
-      </c>
-      <c r="J19" s="22" t="s">
-        <v>490</v>
-      </c>
-      <c r="K19" s="22" t="s">
-        <v>491</v>
-      </c>
-      <c r="L19" s="22" t="s">
-        <v>492</v>
-      </c>
-      <c r="M19" s="22">
-        <v>2</v>
-      </c>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="20" spans="5:15" ht="60" x14ac:dyDescent="0.15">
-      <c r="E20" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F20" s="22">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="G20" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="H20" s="22">
-        <v>4</v>
-      </c>
-      <c r="I20" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="J20" s="22" t="s">
-        <v>242</v>
-      </c>
-      <c r="K20" s="22" t="s">
-        <v>243</v>
-      </c>
-      <c r="L20" s="22" t="s">
-        <v>244</v>
-      </c>
-      <c r="M20" s="22">
-        <v>2</v>
-      </c>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="21" spans="5:15" ht="60" x14ac:dyDescent="0.15">
-      <c r="E21" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F21" s="22">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="G21" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="H21" s="22">
-        <v>4</v>
-      </c>
-      <c r="I21" s="22" t="s">
-        <v>246</v>
-      </c>
-      <c r="J21" s="22" t="s">
-        <v>247</v>
-      </c>
-      <c r="K21" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="L21" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="M21" s="22">
-        <v>2</v>
-      </c>
-      <c r="N21" s="22"/>
-      <c r="O21" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="22" spans="5:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="E22" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F22" s="22">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="G22" s="22" t="s">
-        <v>493</v>
-      </c>
-      <c r="H22" s="22">
-        <v>4</v>
-      </c>
-      <c r="I22" s="22" t="s">
-        <v>494</v>
-      </c>
-      <c r="J22" s="22" t="s">
-        <v>495</v>
-      </c>
-      <c r="K22" s="22" t="s">
-        <v>496</v>
-      </c>
-      <c r="L22" s="22" t="s">
-        <v>497</v>
-      </c>
-      <c r="M22" s="22">
-        <v>2</v>
-      </c>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="23" spans="5:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="E23" s="29" t="s">
-        <v>461</v>
-      </c>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29" t="s">
-        <v>498</v>
-      </c>
-      <c r="H23" s="29">
-        <v>1</v>
-      </c>
-      <c r="I23" s="29" t="s">
-        <v>499</v>
-      </c>
-      <c r="J23" s="29" t="s">
-        <v>500</v>
-      </c>
-      <c r="K23" s="29" t="s">
-        <v>501</v>
-      </c>
-      <c r="L23" s="29" t="s">
-        <v>502</v>
-      </c>
-      <c r="M23" s="29">
-        <v>2</v>
-      </c>
-      <c r="N23" s="29" t="s">
-        <v>482</v>
-      </c>
-      <c r="O23" s="29" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="24" spans="5:15" ht="93" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="E24" s="29" t="s">
-        <v>461</v>
-      </c>
-      <c r="F24" s="29">
-        <v>56</v>
-      </c>
-      <c r="G24" s="29" t="s">
-        <v>503</v>
-      </c>
-      <c r="H24" s="29">
-        <v>3</v>
-      </c>
-      <c r="I24" s="29" t="s">
-        <v>504</v>
-      </c>
-      <c r="J24" s="29" t="s">
-        <v>505</v>
-      </c>
-      <c r="K24" s="29" t="s">
-        <v>506</v>
-      </c>
-      <c r="L24" s="29" t="s">
-        <v>507</v>
-      </c>
-      <c r="M24" s="29">
-        <v>2</v>
-      </c>
-      <c r="N24" s="29" t="s">
-        <v>482</v>
-      </c>
-      <c r="O24" s="29" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="25" spans="5:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="E25" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F25" s="22">
-        <v>19</v>
-      </c>
-      <c r="G25" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="H25" s="22">
-        <v>2</v>
-      </c>
-      <c r="I25" s="22" t="s">
-        <v>266</v>
-      </c>
-      <c r="J25" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="K25" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="L25" s="22" t="s">
-        <v>269</v>
-      </c>
-      <c r="M25" s="22">
-        <v>3</v>
-      </c>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="26" spans="5:15" ht="60" x14ac:dyDescent="0.15">
-      <c r="E26" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F26" s="22">
-        <v>20</v>
-      </c>
-      <c r="G26" s="22" t="s">
-        <v>508</v>
-      </c>
-      <c r="H26" s="22">
-        <v>4</v>
-      </c>
-      <c r="I26" s="22" t="s">
-        <v>509</v>
-      </c>
-      <c r="J26" s="22" t="s">
-        <v>510</v>
-      </c>
-      <c r="K26" s="22" t="s">
-        <v>511</v>
-      </c>
-      <c r="L26" s="22" t="s">
-        <v>512</v>
-      </c>
-      <c r="M26" s="22">
-        <v>3</v>
-      </c>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="27" spans="5:15" ht="75" x14ac:dyDescent="0.15">
-      <c r="E27" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F27" s="22">
-        <v>21</v>
-      </c>
-      <c r="G27" s="22" t="s">
-        <v>513</v>
-      </c>
-      <c r="H27" s="22">
-        <v>2</v>
-      </c>
-      <c r="I27" s="22" t="s">
-        <v>203</v>
-      </c>
-      <c r="J27" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="K27" s="22" t="s">
-        <v>514</v>
-      </c>
-      <c r="L27" s="22" t="s">
-        <v>515</v>
-      </c>
-      <c r="M27" s="22">
-        <v>3</v>
-      </c>
-      <c r="N27" s="22"/>
-      <c r="O27" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="28" spans="5:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="E28" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F28" s="22">
-        <v>22</v>
-      </c>
-      <c r="G28" s="22" t="s">
-        <v>516</v>
-      </c>
-      <c r="H28" s="22">
-        <v>2</v>
-      </c>
-      <c r="I28" s="22" t="s">
-        <v>517</v>
-      </c>
-      <c r="J28" s="22" t="s">
-        <v>518</v>
-      </c>
-      <c r="K28" s="22" t="s">
-        <v>519</v>
-      </c>
-      <c r="L28" s="22" t="s">
-        <v>520</v>
-      </c>
-      <c r="M28" s="22">
-        <v>3</v>
-      </c>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="29" spans="5:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="E29" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="F29" s="22">
-        <v>26</v>
-      </c>
-      <c r="G29" s="22" t="s">
-        <v>521</v>
-      </c>
-      <c r="H29" s="22">
-        <v>4</v>
-      </c>
-      <c r="I29" s="22" t="s">
-        <v>522</v>
-      </c>
-      <c r="J29" s="22" t="s">
-        <v>523</v>
-      </c>
-      <c r="K29" s="22" t="s">
-        <v>524</v>
-      </c>
-      <c r="L29" s="22" t="s">
-        <v>525</v>
-      </c>
-      <c r="M29" s="22">
-        <v>3</v>
-      </c>
-      <c r="N29" s="22"/>
-      <c r="O29" s="22" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="30" spans="5:15" ht="45" x14ac:dyDescent="0.15">
-      <c r="E30" s="29" t="s">
-        <v>461</v>
-      </c>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29" t="s">
-        <v>526</v>
-      </c>
-      <c r="H30" s="29">
-        <v>1</v>
-      </c>
-      <c r="I30" s="29" t="s">
-        <v>527</v>
-      </c>
-      <c r="J30" s="29" t="s">
-        <v>528</v>
-      </c>
-      <c r="K30" s="29" t="s">
-        <v>529</v>
-      </c>
-      <c r="L30" s="29" t="s">
-        <v>530</v>
-      </c>
-      <c r="M30" s="29">
-        <v>3</v>
-      </c>
-      <c r="N30" s="29" t="s">
-        <v>482</v>
-      </c>
-      <c r="O30" s="29" t="s">
-        <v>462</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A6:O6" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A7:O106">
-      <sortCondition ref="M6"/>
-    </sortState>
-  </autoFilter>
-  <mergeCells count="1">
-    <mergeCell ref="F2:L2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="L3:L5">
-    <cfRule type="duplicateValues" dxfId="9" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O3:O5">
-    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
-  </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M7:M13" xr:uid="{00000000-0002-0000-0100-000000000000}">
-      <formula1>"1,2,3"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H7:H13" xr:uid="{00000000-0002-0000-0100-000001000000}">
-      <formula1>"1,2,3,4"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N7:N13" xr:uid="{00000000-0002-0000-0100-000002000000}">
-      <formula1>"Giữ nguyên,X"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
